--- a/data/fmsForecastOutput/File1/RPT_RPT9118491557157QP_fmsForecastOutput.xlsx
+++ b/data/fmsForecastOutput/File1/RPT_RPT9118491557157QP_fmsForecastOutput.xlsx
@@ -1875,40 +1875,40 @@
         </is>
       </c>
       <c r="C8" s="148" t="n">
-        <v>453.7323818790083</v>
+        <v>453.7323818790084</v>
       </c>
       <c r="D8" s="149" t="n">
-        <v>477.8161195224901</v>
+        <v>477.81611952249</v>
       </c>
       <c r="E8" s="149" t="n">
         <v>508.5117584209896</v>
       </c>
       <c r="F8" s="149" t="n">
-        <v>536.7661157221925</v>
+        <v>536.7661157221924</v>
       </c>
       <c r="G8" s="150" t="n">
         <v>564.1004634540959</v>
       </c>
       <c r="H8" s="148" t="n">
-        <v>449.4964055209358</v>
+        <v>449.4964055209775</v>
       </c>
       <c r="I8" s="149" t="n">
-        <v>474.5635455336748</v>
+        <v>474.5635455336746</v>
       </c>
       <c r="J8" s="149" t="n">
         <v>506.1788213564741</v>
       </c>
       <c r="K8" s="149" t="n">
-        <v>535.4044950830055</v>
+        <v>535.4044950830054</v>
       </c>
       <c r="L8" s="150" t="n">
         <v>563.8599622534324</v>
       </c>
       <c r="M8" s="151" t="n">
-        <v>48443317.48582028</v>
+        <v>48443317.48582027</v>
       </c>
       <c r="N8" s="152" t="n">
-        <v>56057872.88373959</v>
+        <v>56057872.88373958</v>
       </c>
       <c r="O8" s="152" t="n">
         <v>64687612.4394739</v>
@@ -1925,40 +1925,40 @@
         </is>
       </c>
       <c r="T8" s="148" t="n">
-        <v>469.3311561503295</v>
+        <v>469.3311561503296</v>
       </c>
       <c r="U8" s="149" t="n">
-        <v>494.2428637649089</v>
+        <v>494.2428637649087</v>
       </c>
       <c r="V8" s="149" t="n">
-        <v>525.9937818575203</v>
+        <v>525.9937818575202</v>
       </c>
       <c r="W8" s="149" t="n">
-        <v>555.2194900239567</v>
+        <v>555.2194900239566</v>
       </c>
       <c r="X8" s="150" t="n">
         <v>583.4935597972053</v>
       </c>
       <c r="Y8" s="148" t="n">
-        <v>465.6736692480497</v>
+        <v>465.6736692480857</v>
       </c>
       <c r="Z8" s="149" t="n">
-        <v>491.4356642878188</v>
+        <v>491.4356642878186</v>
       </c>
       <c r="AA8" s="149" t="n">
         <v>523.9810384304667</v>
       </c>
       <c r="AB8" s="149" t="n">
-        <v>554.0451521575278</v>
+        <v>554.0451521575277</v>
       </c>
       <c r="AC8" s="150" t="n">
         <v>583.2862110127646</v>
       </c>
       <c r="AD8" s="151" t="n">
-        <v>48443317.48582028</v>
+        <v>48443317.48582027</v>
       </c>
       <c r="AE8" s="152" t="n">
-        <v>56057872.88373959</v>
+        <v>56057872.88373958</v>
       </c>
       <c r="AF8" s="152" t="n">
         <v>64687612.4394739</v>
@@ -2028,7 +2028,7 @@
         <v>922.5011236668605</v>
       </c>
       <c r="E9" s="156" t="n">
-        <v>970.5771370632121</v>
+        <v>970.5771370632123</v>
       </c>
       <c r="F9" s="156" t="n">
         <v>1009.617760662079</v>
@@ -2043,10 +2043,10 @@
         <v>915.1597728184979</v>
       </c>
       <c r="J9" s="156" t="n">
-        <v>965.0117861320479</v>
+        <v>965.011786132048</v>
       </c>
       <c r="K9" s="156" t="n">
-        <v>1005.981766253666</v>
+        <v>1005.981766253667</v>
       </c>
       <c r="L9" s="157" t="n">
         <v>1046.953055157396</v>
@@ -2055,13 +2055,13 @@
         <v>20284595.06762622</v>
       </c>
       <c r="N9" s="159" t="n">
-        <v>22558342.41644684</v>
+        <v>22558342.41644685</v>
       </c>
       <c r="O9" s="159" t="n">
-        <v>25407144.36613053</v>
+        <v>25407144.36613054</v>
       </c>
       <c r="P9" s="159" t="n">
-        <v>28372025.05451232</v>
+        <v>28372025.05451233</v>
       </c>
       <c r="Q9" s="160" t="n">
         <v>32431022.39418732</v>
@@ -2078,7 +2078,7 @@
         <v>933.8161536101693</v>
       </c>
       <c r="V9" s="156" t="n">
-        <v>982.4818481648185</v>
+        <v>982.4818481648188</v>
       </c>
       <c r="W9" s="156" t="n">
         <v>1022.001328443307</v>
@@ -2093,7 +2093,7 @@
         <v>926.319989350736</v>
       </c>
       <c r="AA9" s="156" t="n">
-        <v>976.7990248328259</v>
+        <v>976.7990248328261</v>
       </c>
       <c r="AB9" s="156" t="n">
         <v>1018.28851656949</v>
@@ -2105,13 +2105,13 @@
         <v>20284595.06762622</v>
       </c>
       <c r="AE9" s="159" t="n">
-        <v>22558342.41644684</v>
+        <v>22558342.41644685</v>
       </c>
       <c r="AF9" s="159" t="n">
-        <v>25407144.36613053</v>
+        <v>25407144.36613054</v>
       </c>
       <c r="AG9" s="159" t="n">
-        <v>28372025.05451232</v>
+        <v>28372025.05451233</v>
       </c>
       <c r="AH9" s="160" t="n">
         <v>32431022.39418732</v>
@@ -2170,31 +2170,31 @@
         </is>
       </c>
       <c r="C10" s="161" t="n">
-        <v>530.1547633621515</v>
+        <v>530.1547633621516</v>
       </c>
       <c r="D10" s="162" t="n">
-        <v>554.5160055734442</v>
+        <v>554.516005573444</v>
       </c>
       <c r="E10" s="162" t="n">
-        <v>587.3688218566052</v>
+        <v>587.3688218566051</v>
       </c>
       <c r="F10" s="162" t="n">
-        <v>617.1124255378742</v>
+        <v>617.1124255378741</v>
       </c>
       <c r="G10" s="163" t="n">
         <v>645.998999418169</v>
       </c>
       <c r="H10" s="161" t="n">
-        <v>525.1145653025592</v>
+        <v>525.1145653025993</v>
       </c>
       <c r="I10" s="162" t="n">
-        <v>550.6311380611705</v>
+        <v>550.6311380611703</v>
       </c>
       <c r="J10" s="162" t="n">
         <v>584.5590906515858</v>
       </c>
       <c r="K10" s="162" t="n">
-        <v>615.4352528808712</v>
+        <v>615.4352528808711</v>
       </c>
       <c r="L10" s="163" t="n">
         <v>645.6178079755681</v>
@@ -2203,10 +2203,10 @@
         <v>68727912.55344649</v>
       </c>
       <c r="N10" s="165" t="n">
-        <v>78616215.30018644</v>
+        <v>78616215.30018643</v>
       </c>
       <c r="O10" s="165" t="n">
-        <v>90094756.80560443</v>
+        <v>90094756.80560444</v>
       </c>
       <c r="P10" s="165" t="n">
         <v>102060246.5097215</v>
@@ -2220,10 +2220,10 @@
         </is>
       </c>
       <c r="T10" s="161" t="n">
-        <v>546.2754853434667</v>
+        <v>546.2754853434668</v>
       </c>
       <c r="U10" s="162" t="n">
-        <v>571.4265219979911</v>
+        <v>571.426521997991</v>
       </c>
       <c r="V10" s="162" t="n">
         <v>605.3051833089822</v>
@@ -2235,10 +2235,10 @@
         <v>665.7483414636741</v>
       </c>
       <c r="Y10" s="161" t="n">
-        <v>541.7625587797414</v>
+        <v>541.7625587797759</v>
       </c>
       <c r="Z10" s="162" t="n">
-        <v>567.9449225898655</v>
+        <v>567.9449225898654</v>
       </c>
       <c r="AA10" s="162" t="n">
         <v>602.7827405677925</v>
@@ -2253,10 +2253,10 @@
         <v>68727912.55344649</v>
       </c>
       <c r="AE10" s="165" t="n">
-        <v>78616215.30018644</v>
+        <v>78616215.30018643</v>
       </c>
       <c r="AF10" s="165" t="n">
-        <v>90094756.80560443</v>
+        <v>90094756.80560444</v>
       </c>
       <c r="AG10" s="165" t="n">
         <v>102060246.5097215</v>
@@ -2318,13 +2318,13 @@
         </is>
       </c>
       <c r="C11" s="155" t="n">
-        <v>850.0609933811985</v>
+        <v>850.0609933811986</v>
       </c>
       <c r="D11" s="156" t="n">
         <v>881.131792044073</v>
       </c>
       <c r="E11" s="156" t="n">
-        <v>916.5874711014275</v>
+        <v>916.5874711014278</v>
       </c>
       <c r="F11" s="156" t="n">
         <v>944.7441463407799</v>
@@ -2339,7 +2339,7 @@
         <v>878.652144285428</v>
       </c>
       <c r="J11" s="156" t="n">
-        <v>915.6560392100143</v>
+        <v>915.6560392100147</v>
       </c>
       <c r="K11" s="156" t="n">
         <v>944.7441463407799</v>
@@ -2348,13 +2348,13 @@
         <v>966.2765364458008</v>
       </c>
       <c r="M11" s="158" t="n">
-        <v>6878510.999352514</v>
+        <v>6878510.999352515</v>
       </c>
       <c r="N11" s="159" t="n">
         <v>7791328.033578638</v>
       </c>
       <c r="O11" s="159" t="n">
-        <v>8868139.370904427</v>
+        <v>8868139.370904431</v>
       </c>
       <c r="P11" s="159" t="n">
         <v>10057877.14096342</v>
@@ -2374,7 +2374,7 @@
         <v>1080.705952798063</v>
       </c>
       <c r="V11" s="156" t="n">
-        <v>1124.192255033159</v>
+        <v>1124.19225503316</v>
       </c>
       <c r="W11" s="156" t="n">
         <v>1158.726347227903</v>
@@ -2398,13 +2398,13 @@
         <v>1185.135770170734</v>
       </c>
       <c r="AD11" s="158" t="n">
-        <v>6878510.999352514</v>
+        <v>6878510.999352515</v>
       </c>
       <c r="AE11" s="159" t="n">
         <v>7791328.033578638</v>
       </c>
       <c r="AF11" s="159" t="n">
-        <v>8868139.370904427</v>
+        <v>8868139.370904431</v>
       </c>
       <c r="AG11" s="159" t="n">
         <v>10057877.14096342</v>
@@ -2461,31 +2461,31 @@
         </is>
       </c>
       <c r="C12" s="161" t="n">
-        <v>548.9497016548322</v>
+        <v>548.9497016548323</v>
       </c>
       <c r="D12" s="162" t="n">
-        <v>573.6909507917907</v>
+        <v>573.6909507917904</v>
       </c>
       <c r="E12" s="162" t="n">
         <v>606.9027567388093</v>
       </c>
       <c r="F12" s="162" t="n">
-        <v>636.9273366028627</v>
+        <v>636.9273366028626</v>
       </c>
       <c r="G12" s="163" t="n">
         <v>665.8055489039087</v>
       </c>
       <c r="H12" s="161" t="n">
-        <v>543.8847092956677</v>
+        <v>543.8847092957068</v>
       </c>
       <c r="I12" s="162" t="n">
-        <v>569.8123650292849</v>
+        <v>569.8123650292847</v>
       </c>
       <c r="J12" s="162" t="n">
         <v>604.1347661022556</v>
       </c>
       <c r="K12" s="162" t="n">
-        <v>635.3007351654453</v>
+        <v>635.3007351654452</v>
       </c>
       <c r="L12" s="163" t="n">
         <v>665.4369529019586</v>
@@ -2494,10 +2494,10 @@
         <v>75606423.55279902</v>
       </c>
       <c r="N12" s="165" t="n">
-        <v>86407543.33376507</v>
+        <v>86407543.33376506</v>
       </c>
       <c r="O12" s="165" t="n">
-        <v>98962896.17650884</v>
+        <v>98962896.17650887</v>
       </c>
       <c r="P12" s="165" t="n">
         <v>112118123.650685</v>
@@ -2511,13 +2511,13 @@
         </is>
       </c>
       <c r="T12" s="161" t="n">
-        <v>571.0054171648112</v>
+        <v>571.0054171648113</v>
       </c>
       <c r="U12" s="162" t="n">
-        <v>596.785191406832</v>
+        <v>596.7851914068319</v>
       </c>
       <c r="V12" s="162" t="n">
-        <v>631.4214883221684</v>
+        <v>631.4214883221686</v>
       </c>
       <c r="W12" s="162" t="n">
         <v>662.7916373686361</v>
@@ -2526,13 +2526,13 @@
         <v>693.0065319647405</v>
       </c>
       <c r="Y12" s="161" t="n">
-        <v>566.3778224292082</v>
+        <v>566.3778224292423</v>
       </c>
       <c r="Z12" s="162" t="n">
-        <v>593.2393612941519</v>
+        <v>593.2393612941518</v>
       </c>
       <c r="AA12" s="162" t="n">
-        <v>628.887403448283</v>
+        <v>628.8874034482831</v>
       </c>
       <c r="AB12" s="162" t="n">
         <v>661.2962245216662</v>
@@ -2544,10 +2544,10 @@
         <v>75606423.55279902</v>
       </c>
       <c r="AE12" s="165" t="n">
-        <v>86407543.33376507</v>
+        <v>86407543.33376506</v>
       </c>
       <c r="AF12" s="165" t="n">
-        <v>98962896.17650884</v>
+        <v>98962896.17650887</v>
       </c>
       <c r="AG12" s="165" t="n">
         <v>112118123.650685</v>
@@ -2603,46 +2603,46 @@
         </is>
       </c>
       <c r="C13" s="155" t="n">
-        <v>4766.792673747267</v>
+        <v>4766.792673747266</v>
       </c>
       <c r="D13" s="156" t="n">
-        <v>4848.432407797193</v>
+        <v>4848.432407797189</v>
       </c>
       <c r="E13" s="156" t="n">
-        <v>5381.071504192175</v>
+        <v>5381.071504192173</v>
       </c>
       <c r="F13" s="156" t="n">
-        <v>5589.158674949741</v>
+        <v>5589.158674949739</v>
       </c>
       <c r="G13" s="157" t="n">
-        <v>5946.9233581626</v>
+        <v>5946.923358162596</v>
       </c>
       <c r="H13" s="155" t="n">
-        <v>4759.461506208727</v>
+        <v>4759.461506208725</v>
       </c>
       <c r="I13" s="156" t="n">
-        <v>4841.238526563641</v>
+        <v>4841.238526563637</v>
       </c>
       <c r="J13" s="156" t="n">
-        <v>5373.244843865687</v>
+        <v>5373.244843865686</v>
       </c>
       <c r="K13" s="156" t="n">
-        <v>5581.820641199549</v>
+        <v>5581.820641199548</v>
       </c>
       <c r="L13" s="157" t="n">
-        <v>5939.801099897695</v>
+        <v>5939.801099897692</v>
       </c>
       <c r="M13" s="158" t="n">
-        <v>6695828.650701697</v>
+        <v>6695828.650701695</v>
       </c>
       <c r="N13" s="159" t="n">
-        <v>7243139.520317769</v>
+        <v>7243139.520317761</v>
       </c>
       <c r="O13" s="159" t="n">
-        <v>8450119.12970455</v>
+        <v>8450119.129704546</v>
       </c>
       <c r="P13" s="159" t="n">
-        <v>9921924.315029265</v>
+        <v>9921924.315029262</v>
       </c>
       <c r="Q13" s="160" t="n">
         <v>11809165.1540955</v>
@@ -2653,46 +2653,46 @@
         </is>
       </c>
       <c r="T13" s="155" t="n">
-        <v>3880.822982524031</v>
+        <v>3880.822982524029</v>
       </c>
       <c r="U13" s="156" t="n">
-        <v>3947.288922595857</v>
+        <v>3947.288922595852</v>
       </c>
       <c r="V13" s="156" t="n">
-        <v>4380.930196332124</v>
+        <v>4380.930196332122</v>
       </c>
       <c r="W13" s="156" t="n">
-        <v>4550.341691632074</v>
+        <v>4550.341691632072</v>
       </c>
       <c r="X13" s="157" t="n">
-        <v>4841.611209728489</v>
+        <v>4841.611209728486</v>
       </c>
       <c r="Y13" s="155" t="n">
-        <v>3875.039677291379</v>
+        <v>3875.039677291378</v>
       </c>
       <c r="Z13" s="156" t="n">
-        <v>3941.613927359102</v>
+        <v>3941.613927359099</v>
       </c>
       <c r="AA13" s="156" t="n">
-        <v>4374.756029952748</v>
+        <v>4374.756029952746</v>
       </c>
       <c r="AB13" s="156" t="n">
-        <v>4544.553010384677</v>
+        <v>4544.553010384675</v>
       </c>
       <c r="AC13" s="157" t="n">
-        <v>4835.992765262456</v>
+        <v>4835.992765262453</v>
       </c>
       <c r="AD13" s="158" t="n">
-        <v>6695828.650701697</v>
+        <v>6695828.650701695</v>
       </c>
       <c r="AE13" s="159" t="n">
-        <v>7243139.520317769</v>
+        <v>7243139.520317761</v>
       </c>
       <c r="AF13" s="159" t="n">
-        <v>8450119.12970455</v>
+        <v>8450119.129704546</v>
       </c>
       <c r="AG13" s="159" t="n">
-        <v>9921924.315029265</v>
+        <v>9921924.315029262</v>
       </c>
       <c r="AH13" s="160" t="n">
         <v>11809165.1540955</v>
@@ -2746,37 +2746,37 @@
         </is>
       </c>
       <c r="C14" s="167" t="n">
-        <v>591.5326234307502</v>
+        <v>591.5326234307503</v>
       </c>
       <c r="D14" s="168" t="n">
         <v>615.674129235693</v>
       </c>
       <c r="E14" s="168" t="n">
-        <v>652.4409884787705</v>
+        <v>652.4409884787704</v>
       </c>
       <c r="F14" s="168" t="n">
-        <v>686.3705472427979</v>
+        <v>686.3705472427978</v>
       </c>
       <c r="G14" s="169" t="n">
         <v>719.0469839119924</v>
       </c>
       <c r="H14" s="167" t="n">
-        <v>586.1202988364053</v>
+        <v>586.120298836447</v>
       </c>
       <c r="I14" s="168" t="n">
-        <v>611.543446684561</v>
+        <v>611.5434466845609</v>
       </c>
       <c r="J14" s="168" t="n">
-        <v>649.4845771713777</v>
+        <v>649.4845771713776</v>
       </c>
       <c r="K14" s="168" t="n">
-        <v>684.6261697101235</v>
+        <v>684.6261697101232</v>
       </c>
       <c r="L14" s="169" t="n">
         <v>718.6442413931477</v>
       </c>
       <c r="M14" s="170" t="n">
-        <v>82302252.20350072</v>
+        <v>82302252.2035007</v>
       </c>
       <c r="N14" s="171" t="n">
         <v>93650682.85408282</v>
@@ -2796,37 +2796,37 @@
         </is>
       </c>
       <c r="T14" s="167" t="n">
-        <v>613.5793287970733</v>
+        <v>613.5793287970735</v>
       </c>
       <c r="U14" s="168" t="n">
         <v>638.7161705625662</v>
       </c>
       <c r="V14" s="168" t="n">
-        <v>677.0047809187238</v>
+        <v>677.0047809187237</v>
       </c>
       <c r="W14" s="168" t="n">
-        <v>712.264473443966</v>
+        <v>712.2644734439659</v>
       </c>
       <c r="X14" s="169" t="n">
         <v>746.3278344159346</v>
       </c>
       <c r="Y14" s="167" t="n">
-        <v>608.6585622728392</v>
+        <v>608.6585622728757</v>
       </c>
       <c r="Z14" s="168" t="n">
         <v>634.9570462496328</v>
       </c>
       <c r="AA14" s="168" t="n">
-        <v>674.3091331855362</v>
+        <v>674.3091331855361</v>
       </c>
       <c r="AB14" s="168" t="n">
-        <v>710.666349695087</v>
+        <v>710.6663496950869</v>
       </c>
       <c r="AC14" s="169" t="n">
         <v>745.9422402406755</v>
       </c>
       <c r="AD14" s="170" t="n">
-        <v>82302252.20350072</v>
+        <v>82302252.2035007</v>
       </c>
       <c r="AE14" s="171" t="n">
         <v>93650682.85408282</v>
@@ -3167,7 +3167,7 @@
         <v>151993.8782973449</v>
       </c>
       <c r="H19" s="74" t="n">
-        <v>1006.146929380826</v>
+        <v>1006.14692937085</v>
       </c>
       <c r="I19" s="75" t="n">
         <v>804.0973447741715</v>
@@ -3182,16 +3182,16 @@
         <v>64.82941274626535</v>
       </c>
       <c r="M19" s="74" t="n">
-        <v>107772.4246307993</v>
+        <v>107772.4246307893</v>
       </c>
       <c r="N19" s="75" t="n">
-        <v>118125.1139311579</v>
+        <v>118125.113931158</v>
       </c>
       <c r="O19" s="75" t="n">
         <v>127795.9679666604</v>
       </c>
       <c r="P19" s="75" t="n">
-        <v>137630.9353618428</v>
+        <v>137630.9353618429</v>
       </c>
       <c r="Q19" s="76" t="n">
         <v>152058.7077100912</v>
@@ -3202,7 +3202,7 @@
         </is>
       </c>
       <c r="T19" s="74" t="n">
-        <v>103217.7745947546</v>
+        <v>103217.7745947545</v>
       </c>
       <c r="U19" s="75" t="n">
         <v>113421.7142898477</v>
@@ -3211,13 +3211,13 @@
         <v>122981.7056221328</v>
       </c>
       <c r="W19" s="75" t="n">
-        <v>132719.082775768</v>
+        <v>132719.0827757681</v>
       </c>
       <c r="X19" s="76" t="n">
         <v>146942.1825658484</v>
       </c>
       <c r="Y19" s="74" t="n">
-        <v>810.6914425125003</v>
+        <v>810.6914425044615</v>
       </c>
       <c r="Z19" s="75" t="n">
         <v>647.8922882134144</v>
@@ -3232,13 +3232,13 @@
         <v>52.23556182679105</v>
       </c>
       <c r="AD19" s="74" t="n">
-        <v>104028.4660372671</v>
+        <v>104028.466037259</v>
       </c>
       <c r="AE19" s="75" t="n">
         <v>114069.6065780611</v>
       </c>
       <c r="AF19" s="75" t="n">
-        <v>123454.1093953308</v>
+        <v>123454.1093953309</v>
       </c>
       <c r="AG19" s="75" t="n">
         <v>133000.3902538578</v>
@@ -3322,7 +3322,7 @@
         <v>23109.32402884223</v>
       </c>
       <c r="N20" s="80" t="n">
-        <v>24649.62194193909</v>
+        <v>24649.6219419391</v>
       </c>
       <c r="O20" s="80" t="n">
         <v>26328.32544767897</v>
@@ -3342,7 +3342,7 @@
         <v>22594.04452840141</v>
       </c>
       <c r="U20" s="80" t="n">
-        <v>24157.15591258024</v>
+        <v>24157.15591258025</v>
       </c>
       <c r="V20" s="80" t="n">
         <v>25860.16669273701</v>
@@ -3418,13 +3418,13 @@
         <v>153387.0260951633</v>
       </c>
       <c r="F21" s="86" t="n">
-        <v>165383.5545780268</v>
+        <v>165383.5545780269</v>
       </c>
       <c r="G21" s="87" t="n">
         <v>182927.279593835</v>
       </c>
       <c r="H21" s="85" t="n">
-        <v>1244.296913314266</v>
+        <v>1244.296913304289</v>
       </c>
       <c r="I21" s="86" t="n">
         <v>1000.261358359291</v>
@@ -3439,10 +3439,10 @@
         <v>108.0055610889366</v>
       </c>
       <c r="M21" s="85" t="n">
-        <v>130881.7486596416</v>
+        <v>130881.7486596316</v>
       </c>
       <c r="N21" s="86" t="n">
-        <v>142774.735873097</v>
+        <v>142774.7358730971</v>
       </c>
       <c r="O21" s="86" t="n">
         <v>154124.2934143394</v>
@@ -3474,7 +3474,7 @@
         <v>177500.7645142633</v>
       </c>
       <c r="Y21" s="85" t="n">
-        <v>1048.022775568631</v>
+        <v>1048.022775560592</v>
       </c>
       <c r="Z21" s="86" t="n">
         <v>843.3819795115214</v>
@@ -3489,7 +3489,7 @@
         <v>95.26329029079685</v>
       </c>
       <c r="AD21" s="85" t="n">
-        <v>126859.8418987246</v>
+        <v>126859.8418987165</v>
       </c>
       <c r="AE21" s="86" t="n">
         <v>138422.2521819394</v>
@@ -3566,7 +3566,7 @@
         </is>
       </c>
       <c r="C22" s="79" t="n">
-        <v>8091.785240012696</v>
+        <v>8091.785240012697</v>
       </c>
       <c r="D22" s="80" t="n">
         <v>8842.409392020809</v>
@@ -3596,7 +3596,7 @@
         <v>0</v>
       </c>
       <c r="M22" s="79" t="n">
-        <v>8130.108560447517</v>
+        <v>8130.108560447518</v>
       </c>
       <c r="N22" s="80" t="n">
         <v>8867.363591213913</v>
@@ -3616,7 +3616,7 @@
         </is>
       </c>
       <c r="T22" s="79" t="n">
-        <v>6597.473818764502</v>
+        <v>6597.473818764503</v>
       </c>
       <c r="U22" s="80" t="n">
         <v>7209.480074951061</v>
@@ -3646,7 +3646,7 @@
         <v>0</v>
       </c>
       <c r="AD22" s="79" t="n">
-        <v>6631.302278710199</v>
+        <v>6631.3022787102</v>
       </c>
       <c r="AE22" s="80" t="n">
         <v>7231.507449361809</v>
@@ -3712,13 +3712,13 @@
         <v>163062.1958421902</v>
       </c>
       <c r="F23" s="86" t="n">
-        <v>176029.69319653</v>
+        <v>176029.6931965301</v>
       </c>
       <c r="G23" s="87" t="n">
         <v>194985.542673434</v>
       </c>
       <c r="H23" s="85" t="n">
-        <v>1282.620233749088</v>
+        <v>1282.620233739111</v>
       </c>
       <c r="I23" s="86" t="n">
         <v>1025.215557552396</v>
@@ -3733,10 +3733,10 @@
         <v>108.0055610889366</v>
       </c>
       <c r="M23" s="85" t="n">
-        <v>139011.8572200891</v>
+        <v>139011.8572200791</v>
       </c>
       <c r="N23" s="86" t="n">
-        <v>151642.0994643109</v>
+        <v>151642.099464311</v>
       </c>
       <c r="O23" s="86" t="n">
         <v>163809.305024764</v>
@@ -3759,7 +3759,7 @@
         <v>144788.350277379</v>
       </c>
       <c r="V23" s="86" t="n">
-        <v>156730.326741771</v>
+        <v>156730.3267417711</v>
       </c>
       <c r="W23" s="86" t="n">
         <v>169160.4379557467</v>
@@ -3768,7 +3768,7 @@
         <v>187332.2260036323</v>
       </c>
       <c r="Y23" s="85" t="n">
-        <v>1081.851235514328</v>
+        <v>1081.851235506289</v>
       </c>
       <c r="Z23" s="86" t="n">
         <v>865.4093539222695</v>
@@ -3783,7 +3783,7 @@
         <v>95.26329029079685</v>
       </c>
       <c r="AD23" s="85" t="n">
-        <v>133491.1441774348</v>
+        <v>133491.1441774268</v>
       </c>
       <c r="AE23" s="86" t="n">
         <v>145653.7596313012</v>
@@ -3948,7 +3948,7 @@
         <v>152110.7975908329</v>
       </c>
       <c r="E25" s="92" t="n">
-        <v>164632.5371995056</v>
+        <v>164632.5371995057</v>
       </c>
       <c r="F25" s="92" t="n">
         <v>177804.9021129451</v>
@@ -3957,7 +3957,7 @@
         <v>196971.3031150725</v>
       </c>
       <c r="H25" s="91" t="n">
-        <v>1284.783915559088</v>
+        <v>1284.783915549111</v>
       </c>
       <c r="I25" s="92" t="n">
         <v>1027.435451812396</v>
@@ -3966,13 +3966,13 @@
         <v>749.3965394237981</v>
       </c>
       <c r="K25" s="92" t="n">
-        <v>453.0339186077844</v>
+        <v>453.0339186077845</v>
       </c>
       <c r="L25" s="93" t="n">
         <v>110.3866338689366</v>
       </c>
       <c r="M25" s="91" t="n">
-        <v>140418.7030664032</v>
+        <v>140418.7030663932</v>
       </c>
       <c r="N25" s="92" t="n">
         <v>153138.2330426453</v>
@@ -3981,7 +3981,7 @@
         <v>165381.9337389295</v>
       </c>
       <c r="P25" s="92" t="n">
-        <v>178257.9360315528</v>
+        <v>178257.9360315529</v>
       </c>
       <c r="Q25" s="93" t="n">
         <v>197081.6897489414</v>
@@ -4007,7 +4007,7 @@
         <v>189771.324196888</v>
       </c>
       <c r="Y25" s="91" t="n">
-        <v>1084.42625463546</v>
+        <v>1084.426254627421</v>
       </c>
       <c r="Z25" s="92" t="n">
         <v>868.0512720360937</v>
@@ -4022,7 +4022,7 @@
         <v>98.0970285553463</v>
       </c>
       <c r="AD25" s="91" t="n">
-        <v>135219.0822653829</v>
+        <v>135219.0822653748</v>
       </c>
       <c r="AE25" s="92" t="n">
         <v>147491.3671833861</v>
@@ -4408,40 +4408,40 @@
         </is>
       </c>
       <c r="C35" s="148" t="n">
-        <v>466.5108185975144</v>
+        <v>466.5108185975145</v>
       </c>
       <c r="D35" s="149" t="n">
-        <v>502.8297901391588</v>
+        <v>502.8297901391586</v>
       </c>
       <c r="E35" s="149" t="n">
         <v>538.5492284241142</v>
       </c>
       <c r="F35" s="149" t="n">
-        <v>575.685824219633</v>
+        <v>575.6858242196329</v>
       </c>
       <c r="G35" s="150" t="n">
         <v>606.5243587645502</v>
       </c>
       <c r="H35" s="148" t="n">
-        <v>462.1555447019628</v>
+        <v>462.1555447020056</v>
       </c>
       <c r="I35" s="149" t="n">
-        <v>499.4069439240864</v>
+        <v>499.4069439240862</v>
       </c>
       <c r="J35" s="149" t="n">
         <v>536.078486233298</v>
       </c>
       <c r="K35" s="149" t="n">
-        <v>574.2254755184297</v>
+        <v>574.2254755184296</v>
       </c>
       <c r="L35" s="150" t="n">
         <v>606.2657703641412</v>
       </c>
       <c r="M35" s="151" t="n">
-        <v>49807623.6090983</v>
+        <v>49807623.60909829</v>
       </c>
       <c r="N35" s="152" t="n">
-        <v>58992502.14904412</v>
+        <v>58992502.1490441</v>
       </c>
       <c r="O35" s="152" t="n">
         <v>68508669.05428636</v>
@@ -4458,40 +4458,40 @@
         </is>
       </c>
       <c r="T35" s="148" t="n">
-        <v>482.548900173919</v>
+        <v>482.5489001739191</v>
       </c>
       <c r="U35" s="149" t="n">
-        <v>520.1164743312694</v>
+        <v>520.1164743312692</v>
       </c>
       <c r="V35" s="149" t="n">
-        <v>557.0639039987178</v>
+        <v>557.0639039987177</v>
       </c>
       <c r="W35" s="149" t="n">
-        <v>595.4772113496706</v>
+        <v>595.4772113496705</v>
       </c>
       <c r="X35" s="150" t="n">
         <v>627.375937669379</v>
       </c>
       <c r="Y35" s="148" t="n">
-        <v>478.7884076965555</v>
+        <v>478.7884076965925</v>
       </c>
       <c r="Z35" s="149" t="n">
-        <v>517.1623179805908</v>
+        <v>517.1623179805906</v>
       </c>
       <c r="AA35" s="149" t="n">
         <v>554.9322690823075</v>
       </c>
       <c r="AB35" s="149" t="n">
-        <v>594.2177248754961</v>
+        <v>594.2177248754958</v>
       </c>
       <c r="AC35" s="150" t="n">
         <v>627.1529949549672</v>
       </c>
       <c r="AD35" s="151" t="n">
-        <v>49807623.6090983</v>
+        <v>49807623.60909829</v>
       </c>
       <c r="AE35" s="152" t="n">
-        <v>58992502.14904412</v>
+        <v>58992502.1490441</v>
       </c>
       <c r="AF35" s="152" t="n">
         <v>68508669.05428636</v>
@@ -4534,7 +4534,7 @@
         <v>1022.399215977548</v>
       </c>
       <c r="K36" s="156" t="n">
-        <v>1079.329828790576</v>
+        <v>1079.329828790577</v>
       </c>
       <c r="L36" s="157" t="n">
         <v>1126.128183486044</v>
@@ -4543,13 +4543,13 @@
         <v>20863483.19034386</v>
       </c>
       <c r="N36" s="159" t="n">
-        <v>23747974.46079942</v>
+        <v>23747974.46079943</v>
       </c>
       <c r="O36" s="159" t="n">
-        <v>26918059.2957087</v>
+        <v>26918059.29570871</v>
       </c>
       <c r="P36" s="159" t="n">
-        <v>30440683.88890355</v>
+        <v>30440683.88890356</v>
       </c>
       <c r="Q36" s="160" t="n">
         <v>34883596.88856426</v>
@@ -4581,10 +4581,10 @@
         <v>975.1702072573738</v>
       </c>
       <c r="AA36" s="156" t="n">
-        <v>1034.887419520138</v>
+        <v>1034.887419520139</v>
       </c>
       <c r="AB36" s="156" t="n">
-        <v>1092.53388790669</v>
+        <v>1092.533887906691</v>
       </c>
       <c r="AC36" s="157" t="n">
         <v>1139.926861916697</v>
@@ -4593,13 +4593,13 @@
         <v>20863483.19034386</v>
       </c>
       <c r="AE36" s="159" t="n">
-        <v>23747974.46079942</v>
+        <v>23747974.46079943</v>
       </c>
       <c r="AF36" s="159" t="n">
-        <v>26918059.2957087</v>
+        <v>26918059.29570871</v>
       </c>
       <c r="AG36" s="159" t="n">
-        <v>30440683.88890355</v>
+        <v>30440683.88890356</v>
       </c>
       <c r="AH36" s="160" t="n">
         <v>34883596.88856426</v>
@@ -4612,31 +4612,31 @@
         </is>
       </c>
       <c r="C37" s="161" t="n">
-        <v>545.1442144800127</v>
+        <v>545.1442144800129</v>
       </c>
       <c r="D37" s="162" t="n">
-        <v>583.6063007325236</v>
+        <v>583.6063007325233</v>
       </c>
       <c r="E37" s="162" t="n">
         <v>622.1303768598465</v>
       </c>
       <c r="F37" s="162" t="n">
-        <v>661.9271999106533</v>
+        <v>661.9271999106531</v>
       </c>
       <c r="G37" s="163" t="n">
         <v>694.6562958851383</v>
       </c>
       <c r="H37" s="161" t="n">
-        <v>539.9615112357843</v>
+        <v>539.9615112358257</v>
       </c>
       <c r="I37" s="162" t="n">
-        <v>579.5176303697458</v>
+        <v>579.5176303697456</v>
       </c>
       <c r="J37" s="162" t="n">
         <v>619.1543606526392</v>
       </c>
       <c r="K37" s="162" t="n">
-        <v>660.1282307849723</v>
+        <v>660.1282307849722</v>
       </c>
       <c r="L37" s="163" t="n">
         <v>694.2463927184482</v>
@@ -4645,10 +4645,10 @@
         <v>70671106.79944216</v>
       </c>
       <c r="N37" s="165" t="n">
-        <v>82740476.60984354</v>
+        <v>82740476.60984352</v>
       </c>
       <c r="O37" s="165" t="n">
-        <v>95426728.34999506</v>
+        <v>95426728.34999508</v>
       </c>
       <c r="P37" s="165" t="n">
         <v>109471873.193104</v>
@@ -4662,10 +4662,10 @@
         </is>
       </c>
       <c r="T37" s="161" t="n">
-        <v>561.7207293558238</v>
+        <v>561.7207293558239</v>
       </c>
       <c r="U37" s="162" t="n">
-        <v>601.4039546051119</v>
+        <v>601.4039546051118</v>
       </c>
       <c r="V37" s="162" t="n">
         <v>641.1282448001133</v>
@@ -4677,10 +4677,10 @@
         <v>715.8931783011415</v>
       </c>
       <c r="Y37" s="161" t="n">
-        <v>557.0802055378617</v>
+        <v>557.0802055378972</v>
       </c>
       <c r="Z37" s="162" t="n">
-        <v>597.7397080715831</v>
+        <v>597.739708071583</v>
       </c>
       <c r="AA37" s="162" t="n">
         <v>638.4565193104568</v>
@@ -4695,10 +4695,10 @@
         <v>70671106.79944216</v>
       </c>
       <c r="AE37" s="165" t="n">
-        <v>82740476.60984354</v>
+        <v>82740476.60984352</v>
       </c>
       <c r="AF37" s="165" t="n">
-        <v>95426728.34999506</v>
+        <v>95426728.34999508</v>
       </c>
       <c r="AG37" s="165" t="n">
         <v>109471873.193104</v>
@@ -4714,13 +4714,13 @@
         </is>
       </c>
       <c r="C38" s="155" t="n">
-        <v>874.175903151487</v>
+        <v>874.1759031514871</v>
       </c>
       <c r="D38" s="156" t="n">
         <v>927.4499101757548</v>
       </c>
       <c r="E38" s="156" t="n">
-        <v>970.9405499143443</v>
+        <v>970.9405499143446</v>
       </c>
       <c r="F38" s="156" t="n">
         <v>1013.467471736314</v>
@@ -4735,7 +4735,7 @@
         <v>924.8399157211365</v>
       </c>
       <c r="J38" s="156" t="n">
-        <v>969.9538846790344</v>
+        <v>969.9538846790348</v>
       </c>
       <c r="K38" s="156" t="n">
         <v>1013.467471736314</v>
@@ -4750,7 +4750,7 @@
         <v>8200891.79636695</v>
       </c>
       <c r="O38" s="159" t="n">
-        <v>9394014.63469293</v>
+        <v>9394014.634692933</v>
       </c>
       <c r="P38" s="159" t="n">
         <v>10789515.18944878</v>
@@ -4785,7 +4785,7 @@
         <v>1134.050106951171</v>
       </c>
       <c r="AA38" s="156" t="n">
-        <v>1189.546127358325</v>
+        <v>1189.546127358326</v>
       </c>
       <c r="AB38" s="156" t="n">
         <v>1243.01533500661</v>
@@ -4800,7 +4800,7 @@
         <v>8200891.79636695</v>
       </c>
       <c r="AF38" s="159" t="n">
-        <v>9394014.63469293</v>
+        <v>9394014.634692933</v>
       </c>
       <c r="AG38" s="159" t="n">
         <v>10789515.18944878</v>
@@ -4816,31 +4816,31 @@
         </is>
       </c>
       <c r="C39" s="161" t="n">
-        <v>564.4752862273452</v>
+        <v>564.4752862273454</v>
       </c>
       <c r="D39" s="162" t="n">
-        <v>603.7926562237801</v>
+        <v>603.79265622378</v>
       </c>
       <c r="E39" s="162" t="n">
         <v>642.8267597115664</v>
       </c>
       <c r="F39" s="162" t="n">
-        <v>683.1880815033053</v>
+        <v>683.1880815033052</v>
       </c>
       <c r="G39" s="163" t="n">
         <v>715.9628618009061</v>
       </c>
       <c r="H39" s="161" t="n">
-        <v>559.2670440094154</v>
+        <v>559.2670440094556</v>
       </c>
       <c r="I39" s="162" t="n">
-        <v>599.7105601113996</v>
+        <v>599.7105601113993</v>
       </c>
       <c r="J39" s="162" t="n">
-        <v>639.8949251926905</v>
+        <v>639.8949251926906</v>
       </c>
       <c r="K39" s="162" t="n">
-        <v>681.443338184033</v>
+        <v>681.4433381840329</v>
       </c>
       <c r="L39" s="163" t="n">
         <v>715.5664982547642</v>
@@ -4849,7 +4849,7 @@
         <v>77744750.46973813</v>
       </c>
       <c r="N39" s="165" t="n">
-        <v>90941368.40621048</v>
+        <v>90941368.40621047</v>
       </c>
       <c r="O39" s="165" t="n">
         <v>104820742.984688</v>
@@ -4866,13 +4866,13 @@
         </is>
       </c>
       <c r="T39" s="161" t="n">
-        <v>587.1547890814566</v>
+        <v>587.1547890814568</v>
       </c>
       <c r="U39" s="162" t="n">
-        <v>628.0986573297446</v>
+        <v>628.0986573297445</v>
       </c>
       <c r="V39" s="162" t="n">
-        <v>668.7968127405916</v>
+        <v>668.7968127405917</v>
       </c>
       <c r="W39" s="162" t="n">
         <v>710.9309353645314</v>
@@ -4881,13 +4881,13 @@
         <v>745.2129840146545</v>
       </c>
       <c r="Y39" s="161" t="n">
-        <v>582.396315117359</v>
+        <v>582.3963151173941</v>
       </c>
       <c r="Z39" s="162" t="n">
-        <v>624.366776638061</v>
+        <v>624.3667766380609</v>
       </c>
       <c r="AA39" s="162" t="n">
-        <v>666.112729417149</v>
+        <v>666.1127294171491</v>
       </c>
       <c r="AB39" s="162" t="n">
         <v>709.3269090097734</v>
@@ -4899,7 +4899,7 @@
         <v>77744750.46973813</v>
       </c>
       <c r="AE39" s="165" t="n">
-        <v>90941368.40621048</v>
+        <v>90941368.40621047</v>
       </c>
       <c r="AF39" s="165" t="n">
         <v>104820742.984688</v>
@@ -4918,49 +4918,49 @@
         </is>
       </c>
       <c r="C40" s="155" t="n">
-        <v>4903.09882097024</v>
+        <v>4903.098820970239</v>
       </c>
       <c r="D40" s="156" t="n">
-        <v>5104.15033982229</v>
+        <v>5104.150339822286</v>
       </c>
       <c r="E40" s="156" t="n">
-        <v>5701.495554346445</v>
+        <v>5701.495554346443</v>
       </c>
       <c r="F40" s="156" t="n">
-        <v>5996.951367971826</v>
+        <v>5996.951367971824</v>
       </c>
       <c r="G40" s="157" t="n">
-        <v>6396.604666196193</v>
+        <v>6396.604666196188</v>
       </c>
       <c r="H40" s="155" t="n">
-        <v>4895.558019140843</v>
+        <v>4895.558019140841</v>
       </c>
       <c r="I40" s="156" t="n">
-        <v>5096.577036070787</v>
+        <v>5096.577036070783</v>
       </c>
       <c r="J40" s="156" t="n">
-        <v>5693.202843680533</v>
+        <v>5693.202843680531</v>
       </c>
       <c r="K40" s="156" t="n">
-        <v>5989.077941201233</v>
+        <v>5989.077941201232</v>
       </c>
       <c r="L40" s="157" t="n">
-        <v>6388.94385274572</v>
+        <v>6388.943852745716</v>
       </c>
       <c r="M40" s="158" t="n">
-        <v>6887295.46461808</v>
+        <v>6887295.464618078</v>
       </c>
       <c r="N40" s="159" t="n">
-        <v>7625160.038233255</v>
+        <v>7625160.038233248</v>
       </c>
       <c r="O40" s="159" t="n">
-        <v>8953294.267540315</v>
+        <v>8953294.267540311</v>
       </c>
       <c r="P40" s="159" t="n">
         <v>10645841.53973097</v>
       </c>
       <c r="Q40" s="160" t="n">
-        <v>12702124.50693289</v>
+        <v>12702124.50693288</v>
       </c>
       <c r="S40" s="32" t="inlineStr">
         <is>
@@ -4968,49 +4968,49 @@
         </is>
       </c>
       <c r="T40" s="155" t="n">
-        <v>3991.794880193408</v>
+        <v>3991.794880193406</v>
       </c>
       <c r="U40" s="156" t="n">
-        <v>4155.478389931421</v>
+        <v>4155.478389931416</v>
       </c>
       <c r="V40" s="156" t="n">
-        <v>4641.799318003946</v>
+        <v>4641.799318003944</v>
       </c>
       <c r="W40" s="156" t="n">
-        <v>4882.340870849865</v>
+        <v>4882.340870849863</v>
       </c>
       <c r="X40" s="157" t="n">
-        <v>5207.713466417649</v>
+        <v>5207.713466417646</v>
       </c>
       <c r="Y40" s="155" t="n">
         <v>3985.8462016986</v>
       </c>
       <c r="Z40" s="156" t="n">
-        <v>4149.504081860304</v>
+        <v>4149.5040818603</v>
       </c>
       <c r="AA40" s="156" t="n">
-        <v>4635.257501539254</v>
+        <v>4635.257501539252</v>
       </c>
       <c r="AB40" s="156" t="n">
-        <v>4876.129839468537</v>
+        <v>4876.129839468535</v>
       </c>
       <c r="AC40" s="157" t="n">
-        <v>5201.670178834523</v>
+        <v>5201.67017883452</v>
       </c>
       <c r="AD40" s="158" t="n">
-        <v>6887295.46461808</v>
+        <v>6887295.464618078</v>
       </c>
       <c r="AE40" s="159" t="n">
-        <v>7625160.038233255</v>
+        <v>7625160.038233248</v>
       </c>
       <c r="AF40" s="159" t="n">
-        <v>8953294.267540315</v>
+        <v>8953294.267540311</v>
       </c>
       <c r="AG40" s="159" t="n">
         <v>10645841.53973097</v>
       </c>
       <c r="AH40" s="160" t="n">
-        <v>12702124.50693289</v>
+        <v>12702124.50693288</v>
       </c>
     </row>
     <row r="41" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -5020,40 +5020,40 @@
         </is>
       </c>
       <c r="C41" s="179" t="n">
-        <v>608.2775965118981</v>
+        <v>608.2775965118982</v>
       </c>
       <c r="D41" s="180" t="n">
-        <v>647.9916613781789</v>
+        <v>647.9916613781788</v>
       </c>
       <c r="E41" s="180" t="n">
-        <v>691.0786846123511</v>
+        <v>691.078684612351</v>
       </c>
       <c r="F41" s="180" t="n">
         <v>736.2408368197237</v>
       </c>
       <c r="G41" s="181" t="n">
-        <v>773.2320863015747</v>
+        <v>773.2320863015746</v>
       </c>
       <c r="H41" s="179" t="n">
-        <v>602.7120610445618</v>
+        <v>602.7120610446046</v>
       </c>
       <c r="I41" s="180" t="n">
-        <v>643.6441539520398</v>
+        <v>643.6441539520396</v>
       </c>
       <c r="J41" s="180" t="n">
-        <v>687.9471939893451</v>
+        <v>687.947193989345</v>
       </c>
       <c r="K41" s="180" t="n">
-        <v>734.369716359289</v>
+        <v>734.3697163592889</v>
       </c>
       <c r="L41" s="181" t="n">
-        <v>772.7989943826094</v>
+        <v>772.7989943826093</v>
       </c>
       <c r="M41" s="182" t="n">
-        <v>84632045.93435621</v>
+        <v>84632045.9343562</v>
       </c>
       <c r="N41" s="183" t="n">
-        <v>98566528.44444373</v>
+        <v>98566528.44444372</v>
       </c>
       <c r="O41" s="183" t="n">
         <v>113774037.2522283</v>
@@ -5062,7 +5062,7 @@
         <v>130907229.9222838</v>
       </c>
       <c r="Q41" s="184" t="n">
-        <v>152304531.6492074</v>
+        <v>152304531.6492073</v>
       </c>
       <c r="S41" s="51" t="inlineStr">
         <is>
@@ -5070,40 +5070,40 @@
         </is>
       </c>
       <c r="T41" s="185" t="n">
-        <v>630.9483950782649</v>
+        <v>630.948395078265</v>
       </c>
       <c r="U41" s="186" t="n">
-        <v>672.243209286292</v>
+        <v>672.2432092862919</v>
       </c>
       <c r="V41" s="186" t="n">
-        <v>717.0971501414311</v>
+        <v>717.097150141431</v>
       </c>
       <c r="W41" s="186" t="n">
-        <v>764.0161630942534</v>
+        <v>764.0161630942533</v>
       </c>
       <c r="X41" s="187" t="n">
-        <v>802.5687352594492</v>
+        <v>802.5687352594491</v>
       </c>
       <c r="Y41" s="185" t="n">
-        <v>625.8883325968458</v>
+        <v>625.8883325968832</v>
       </c>
       <c r="Z41" s="186" t="n">
         <v>668.2867636713222</v>
       </c>
       <c r="AA41" s="186" t="n">
-        <v>714.2418655677671</v>
+        <v>714.241865567767</v>
       </c>
       <c r="AB41" s="186" t="n">
-        <v>762.301922920425</v>
+        <v>762.3019229204249</v>
       </c>
       <c r="AC41" s="187" t="n">
-        <v>802.1540839289072</v>
+        <v>802.1540839289071</v>
       </c>
       <c r="AD41" s="188" t="n">
-        <v>84632045.93435621</v>
+        <v>84632045.9343562</v>
       </c>
       <c r="AE41" s="189" t="n">
-        <v>98566528.44444373</v>
+        <v>98566528.44444372</v>
       </c>
       <c r="AF41" s="189" t="n">
         <v>113774037.2522283</v>
@@ -5112,7 +5112,7 @@
         <v>130907229.9222838</v>
       </c>
       <c r="AH41" s="190" t="n">
-        <v>152304531.6492074</v>
+        <v>152304531.6492073</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" thickBot="1"/>
@@ -5371,10 +5371,10 @@
         </is>
       </c>
       <c r="C46" s="148" t="n">
-        <v>0.1713538103053007</v>
+        <v>0.1713538103053006</v>
       </c>
       <c r="D46" s="149" t="n">
-        <v>0.1841154846545519</v>
+        <v>0.1841154846545518</v>
       </c>
       <c r="E46" s="149" t="n">
         <v>0.2012688125870582</v>
@@ -5386,22 +5386,22 @@
         <v>0.2387293997620356</v>
       </c>
       <c r="H46" s="148" t="n">
-        <v>0.1697540772505141</v>
+        <v>0.1697540772505298</v>
       </c>
       <c r="I46" s="149" t="n">
-        <v>0.1828621798541111</v>
+        <v>0.182862179854111</v>
       </c>
       <c r="J46" s="149" t="n">
         <v>0.2003454367456158</v>
       </c>
       <c r="K46" s="149" t="n">
-        <v>0.2210237254653181</v>
+        <v>0.221023725465318</v>
       </c>
       <c r="L46" s="150" t="n">
         <v>0.2386276187655711</v>
       </c>
       <c r="M46" s="151" t="n">
-        <v>18294.80849625192</v>
+        <v>18294.80849625191</v>
       </c>
       <c r="N46" s="152" t="n">
         <v>21600.61582896677</v>
@@ -5436,7 +5436,7 @@
         <v>0.2469366297670763</v>
       </c>
       <c r="Y46" s="148" t="n">
-        <v>0.1758634842284227</v>
+        <v>0.1758634842284362</v>
       </c>
       <c r="Z46" s="149" t="n">
         <v>0.1893634639143324</v>
@@ -5445,13 +5445,13 @@
         <v>0.2073915493134459</v>
       </c>
       <c r="AB46" s="149" t="n">
-        <v>0.2287188933422588</v>
+        <v>0.2287188933422587</v>
       </c>
       <c r="AC46" s="150" t="n">
         <v>0.2468488789956131</v>
       </c>
       <c r="AD46" s="151" t="n">
-        <v>18294.80849625192</v>
+        <v>18294.80849625191</v>
       </c>
       <c r="AE46" s="152" t="n">
         <v>21600.61582896677</v>
@@ -5476,7 +5476,7 @@
         <v>0.02957062747023871</v>
       </c>
       <c r="D47" s="156" t="n">
-        <v>0.02864489004090478</v>
+        <v>0.02864489004090477</v>
       </c>
       <c r="E47" s="156" t="n">
         <v>0.02778923529773249</v>
@@ -5541,7 +5541,7 @@
         <v>0.02962217308290659</v>
       </c>
       <c r="Z47" s="156" t="n">
-        <v>0.02876347091282912</v>
+        <v>0.02876347091282911</v>
       </c>
       <c r="AA47" s="156" t="n">
         <v>0.02796737827743326</v>
@@ -5590,13 +5590,13 @@
         <v>0.2026625772621435</v>
       </c>
       <c r="H48" s="161" t="n">
-        <v>0.1449485788356586</v>
+        <v>0.1449485788356696</v>
       </c>
       <c r="I48" s="162" t="n">
         <v>0.15619767955492</v>
       </c>
       <c r="J48" s="162" t="n">
-        <v>0.1708412552676225</v>
+        <v>0.1708412552676224</v>
       </c>
       <c r="K48" s="162" t="n">
         <v>0.1879973077606336</v>
@@ -5605,7 +5605,7 @@
         <v>0.2025429900178021</v>
       </c>
       <c r="M48" s="164" t="n">
-        <v>18971.12346374091</v>
+        <v>18971.1234637409</v>
       </c>
       <c r="N48" s="165" t="n">
         <v>22301.08244244436</v>
@@ -5631,7 +5631,7 @@
         <v>0.162096711578104</v>
       </c>
       <c r="V48" s="162" t="n">
-        <v>0.1769044378751111</v>
+        <v>0.176904437875111</v>
       </c>
       <c r="W48" s="162" t="n">
         <v>0.1942692581774165</v>
@@ -5640,13 +5640,13 @@
         <v>0.2088583338527553</v>
       </c>
       <c r="Y48" s="161" t="n">
-        <v>0.1495439626898324</v>
+        <v>0.1495439626898419</v>
       </c>
       <c r="Z48" s="162" t="n">
         <v>0.1611090853595726</v>
       </c>
       <c r="AA48" s="162" t="n">
-        <v>0.1761672373232127</v>
+        <v>0.1761672373232126</v>
       </c>
       <c r="AB48" s="162" t="n">
         <v>0.1938072898705684</v>
@@ -5655,7 +5655,7 @@
         <v>0.2087463013240246</v>
       </c>
       <c r="AD48" s="164" t="n">
-        <v>18971.12346374091</v>
+        <v>18971.1234637409</v>
       </c>
       <c r="AE48" s="165" t="n">
         <v>22301.08244244436</v>
@@ -5683,7 +5683,7 @@
         <v>0.1633912871997914</v>
       </c>
       <c r="E49" s="156" t="n">
-        <v>0.1639670431477857</v>
+        <v>0.1639670431477858</v>
       </c>
       <c r="F49" s="156" t="n">
         <v>0.1645350746210813</v>
@@ -5698,7 +5698,7 @@
         <v>0.1629314776199473</v>
       </c>
       <c r="J49" s="156" t="n">
-        <v>0.1638004206071732</v>
+        <v>0.1638004206071733</v>
       </c>
       <c r="K49" s="156" t="n">
         <v>0.1645350746210813</v>
@@ -5733,7 +5733,7 @@
         <v>0.2003990076246396</v>
       </c>
       <c r="V49" s="156" t="n">
-        <v>0.2011051708637538</v>
+        <v>0.2011051708637539</v>
       </c>
       <c r="W49" s="156" t="n">
         <v>0.20180186005385</v>
@@ -5779,7 +5779,7 @@
         </is>
       </c>
       <c r="C50" s="161" t="n">
-        <v>0.1473661777332254</v>
+        <v>0.1473661777332253</v>
       </c>
       <c r="D50" s="162" t="n">
         <v>0.1576573255203869</v>
@@ -5794,7 +5794,7 @@
         <v>0.2001022769274538</v>
       </c>
       <c r="H50" s="161" t="n">
-        <v>0.1460064747185995</v>
+        <v>0.1460064747186099</v>
       </c>
       <c r="I50" s="162" t="n">
         <v>0.1565914424743424</v>
@@ -5844,13 +5844,13 @@
         <v>0.2082773043871951</v>
       </c>
       <c r="Y50" s="161" t="n">
-        <v>0.1520447767667079</v>
+        <v>0.152044776766717</v>
       </c>
       <c r="Z50" s="162" t="n">
         <v>0.1630294690302737</v>
       </c>
       <c r="AA50" s="162" t="n">
-        <v>0.1774076349934722</v>
+        <v>0.1774076349934721</v>
       </c>
       <c r="AB50" s="162" t="n">
         <v>0.1942165889670061</v>
@@ -5992,19 +5992,19 @@
         <v>0.1695727782879473</v>
       </c>
       <c r="F52" s="180" t="n">
-        <v>0.1851920630343872</v>
+        <v>0.1851920630343871</v>
       </c>
       <c r="G52" s="181" t="n">
         <v>0.1980849516647367</v>
       </c>
       <c r="H52" s="179" t="n">
-        <v>0.1445436453518043</v>
+        <v>0.1445436453518145</v>
       </c>
       <c r="I52" s="180" t="n">
         <v>0.1550615716477642</v>
       </c>
       <c r="J52" s="180" t="n">
-        <v>0.168804391739571</v>
+        <v>0.1688043917395709</v>
       </c>
       <c r="K52" s="180" t="n">
         <v>0.1847214063675408</v>
@@ -6048,7 +6048,7 @@
         <v>0.2056003520131898</v>
       </c>
       <c r="Y52" s="185" t="n">
-        <v>0.1501018264342013</v>
+        <v>0.1501018264342103</v>
       </c>
       <c r="Z52" s="186" t="n">
         <v>0.1609982709389989</v>
@@ -6337,7 +6337,7 @@
         <v>0.009767608927579389</v>
       </c>
       <c r="D57" s="149" t="n">
-        <v>0.008745544064354757</v>
+        <v>0.008745544064354759</v>
       </c>
       <c r="E57" s="149" t="n">
         <v>0.007944794222633996</v>
@@ -6349,7 +6349,7 @@
         <v>0</v>
       </c>
       <c r="H57" s="148" t="n">
-        <v>0.00967642001943759</v>
+        <v>0.009676420019438487</v>
       </c>
       <c r="I57" s="149" t="n">
         <v>0.008686011687820065</v>
@@ -6364,7 +6364,7 @@
         <v>0</v>
       </c>
       <c r="M57" s="151" t="n">
-        <v>1042.851247240796</v>
+        <v>1042.851247240795</v>
       </c>
       <c r="N57" s="152" t="n">
         <v>1026.036120231115</v>
@@ -6373,7 +6373,7 @@
         <v>1010.654642836487</v>
       </c>
       <c r="P57" s="152" t="n">
-        <v>39.44645797619314</v>
+        <v>39.44645797619315</v>
       </c>
       <c r="Q57" s="153" t="n">
         <v>0</v>
@@ -6384,22 +6384,22 @@
         </is>
       </c>
       <c r="T57" s="148" t="n">
-        <v>0.01010340758977952</v>
+        <v>0.01010340758977953</v>
       </c>
       <c r="U57" s="149" t="n">
-        <v>0.009046205364248799</v>
+        <v>0.009046205364248801</v>
       </c>
       <c r="V57" s="149" t="n">
         <v>0.008217926704820404</v>
       </c>
       <c r="W57" s="149" t="n">
-        <v>0.0002972176807674209</v>
+        <v>0.000297217680767421</v>
       </c>
       <c r="X57" s="150" t="n">
         <v>0</v>
       </c>
       <c r="Y57" s="148" t="n">
-        <v>0.01002467196687496</v>
+        <v>0.01002467196687574</v>
       </c>
       <c r="Z57" s="149" t="n">
         <v>0.008994824747896093</v>
@@ -6408,13 +6408,13 @@
         <v>0.008186480367373747</v>
       </c>
       <c r="AB57" s="149" t="n">
-        <v>0.0002965890393321531</v>
+        <v>0.0002965890393321532</v>
       </c>
       <c r="AC57" s="150" t="n">
         <v>0</v>
       </c>
       <c r="AD57" s="151" t="n">
-        <v>1042.851247240796</v>
+        <v>1042.851247240795</v>
       </c>
       <c r="AE57" s="152" t="n">
         <v>1026.036120231115</v>
@@ -6423,7 +6423,7 @@
         <v>1010.654642836487</v>
       </c>
       <c r="AG57" s="152" t="n">
-        <v>39.44645797619314</v>
+        <v>39.44645797619315</v>
       </c>
       <c r="AH57" s="153" t="n">
         <v>0</v>
@@ -6544,7 +6544,7 @@
         <v>0.007237100498823969</v>
       </c>
       <c r="E59" s="162" t="n">
-        <v>0.006588918688660563</v>
+        <v>0.006588918688660562</v>
       </c>
       <c r="F59" s="162" t="n">
         <v>0.0002385149967107677</v>
@@ -6553,13 +6553,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="161" t="n">
-        <v>0.007967889013713697</v>
+        <v>0.007967889013714306</v>
       </c>
       <c r="I59" s="162" t="n">
         <v>0.00718639830749251</v>
       </c>
       <c r="J59" s="162" t="n">
-        <v>0.006557400007794346</v>
+        <v>0.006557400007794345</v>
       </c>
       <c r="K59" s="162" t="n">
         <v>0.0002378667666408257</v>
@@ -6568,7 +6568,7 @@
         <v>0</v>
       </c>
       <c r="M59" s="164" t="n">
-        <v>1042.851247240796</v>
+        <v>1042.851247240795</v>
       </c>
       <c r="N59" s="165" t="n">
         <v>1026.036120231115</v>
@@ -6577,7 +6577,7 @@
         <v>1010.654642836487</v>
       </c>
       <c r="P59" s="165" t="n">
-        <v>39.44645797619314</v>
+        <v>39.44645797619315</v>
       </c>
       <c r="Q59" s="166" t="n">
         <v>0</v>
@@ -6591,22 +6591,22 @@
         <v>0.00828897677904139</v>
       </c>
       <c r="U59" s="162" t="n">
-        <v>0.007457803067589138</v>
+        <v>0.007457803067589139</v>
       </c>
       <c r="V59" s="162" t="n">
-        <v>0.006790123149609958</v>
+        <v>0.006790123149609957</v>
       </c>
       <c r="W59" s="162" t="n">
-        <v>0.0002458024577629095</v>
+        <v>0.0002458024577629096</v>
       </c>
       <c r="X59" s="163" t="n">
         <v>0</v>
       </c>
       <c r="Y59" s="161" t="n">
-        <v>0.008220499345043562</v>
+        <v>0.008220499345044083</v>
       </c>
       <c r="Z59" s="162" t="n">
-        <v>0.007412364009816235</v>
+        <v>0.007412364009816237</v>
       </c>
       <c r="AA59" s="162" t="n">
         <v>0.006761827180365339</v>
@@ -6618,7 +6618,7 @@
         <v>0</v>
       </c>
       <c r="AD59" s="164" t="n">
-        <v>1042.851247240796</v>
+        <v>1042.851247240795</v>
       </c>
       <c r="AE59" s="165" t="n">
         <v>1026.036120231115</v>
@@ -6627,7 +6627,7 @@
         <v>1010.654642836487</v>
       </c>
       <c r="AG59" s="165" t="n">
-        <v>39.44645797619314</v>
+        <v>39.44645797619315</v>
       </c>
       <c r="AH59" s="166" t="n">
         <v>0</v>
@@ -6748,31 +6748,31 @@
         <v>0.00681222512123074</v>
       </c>
       <c r="E61" s="162" t="n">
-        <v>0.006197970275186208</v>
+        <v>0.006197970275186207</v>
       </c>
       <c r="F61" s="162" t="n">
-        <v>0.0002240897956468785</v>
+        <v>0.0002240897956468786</v>
       </c>
       <c r="G61" s="163" t="n">
         <v>0</v>
       </c>
       <c r="H61" s="161" t="n">
-        <v>0.007501887019534687</v>
+        <v>0.007501887019535225</v>
       </c>
       <c r="I61" s="162" t="n">
         <v>0.006766169314825352</v>
       </c>
       <c r="J61" s="162" t="n">
-        <v>0.006169702280854561</v>
+        <v>0.00616970228085456</v>
       </c>
       <c r="K61" s="162" t="n">
-        <v>0.0002235175093549226</v>
+        <v>0.0002235175093549227</v>
       </c>
       <c r="L61" s="163" t="n">
         <v>0</v>
       </c>
       <c r="M61" s="164" t="n">
-        <v>1042.851247240796</v>
+        <v>1042.851247240795</v>
       </c>
       <c r="N61" s="165" t="n">
         <v>1026.036120231115</v>
@@ -6781,7 +6781,7 @@
         <v>1010.654642836487</v>
       </c>
       <c r="P61" s="165" t="n">
-        <v>39.44645797619314</v>
+        <v>39.44645797619315</v>
       </c>
       <c r="Q61" s="166" t="n">
         <v>0</v>
@@ -6795,34 +6795,34 @@
         <v>0.007875967192863329</v>
       </c>
       <c r="U61" s="162" t="n">
-        <v>0.007086454941060389</v>
+        <v>0.007086454941060391</v>
       </c>
       <c r="V61" s="162" t="n">
-        <v>0.006448366846715263</v>
+        <v>0.006448366846715262</v>
       </c>
       <c r="W61" s="162" t="n">
-        <v>0.0002331896184054131</v>
+        <v>0.0002331896184054132</v>
       </c>
       <c r="X61" s="163" t="n">
         <v>0</v>
       </c>
       <c r="Y61" s="161" t="n">
-        <v>0.007812138053552454</v>
+        <v>0.007812138053552924</v>
       </c>
       <c r="Z61" s="162" t="n">
-        <v>0.007044350402134197</v>
+        <v>0.007044350402134199</v>
       </c>
       <c r="AA61" s="162" t="n">
-        <v>0.006422487605685713</v>
+        <v>0.006422487605685712</v>
       </c>
       <c r="AB61" s="162" t="n">
-        <v>0.0002326634881233113</v>
+        <v>0.0002326634881233114</v>
       </c>
       <c r="AC61" s="163" t="n">
         <v>0</v>
       </c>
       <c r="AD61" s="164" t="n">
-        <v>1042.851247240796</v>
+        <v>1042.851247240795</v>
       </c>
       <c r="AE61" s="165" t="n">
         <v>1026.036120231115</v>
@@ -6831,7 +6831,7 @@
         <v>1010.654642836487</v>
       </c>
       <c r="AG61" s="165" t="n">
-        <v>39.44645797619314</v>
+        <v>39.44645797619315</v>
       </c>
       <c r="AH61" s="166" t="n">
         <v>0</v>
@@ -6946,10 +6946,10 @@
         </is>
       </c>
       <c r="C63" s="179" t="n">
-        <v>0.007495305627883397</v>
+        <v>0.007495305627883399</v>
       </c>
       <c r="D63" s="180" t="n">
-        <v>0.006745320756196925</v>
+        <v>0.006745320756196927</v>
       </c>
       <c r="E63" s="180" t="n">
         <v>0.00613885116531826</v>
@@ -6961,7 +6961,7 @@
         <v>0</v>
       </c>
       <c r="H63" s="179" t="n">
-        <v>0.007426726101776037</v>
+        <v>0.007426726101776564</v>
       </c>
       <c r="I63" s="180" t="n">
         <v>0.006700065031737622</v>
@@ -6976,7 +6976,7 @@
         <v>0</v>
       </c>
       <c r="M63" s="182" t="n">
-        <v>1042.851247240796</v>
+        <v>1042.851247240795</v>
       </c>
       <c r="N63" s="183" t="n">
         <v>1026.036120231115</v>
@@ -6985,7 +6985,7 @@
         <v>1010.654642836487</v>
       </c>
       <c r="P63" s="183" t="n">
-        <v>39.44645797619314</v>
+        <v>39.44645797619315</v>
       </c>
       <c r="Q63" s="184" t="n">
         <v>0</v>
@@ -6996,25 +6996,25 @@
         </is>
       </c>
       <c r="T63" s="185" t="n">
-        <v>0.00777465927341878</v>
+        <v>0.007774659273418782</v>
       </c>
       <c r="U63" s="186" t="n">
-        <v>0.006997769173706774</v>
+        <v>0.006997769173706776</v>
       </c>
       <c r="V63" s="186" t="n">
-        <v>0.006369973164866806</v>
+        <v>0.006369973164866805</v>
       </c>
       <c r="W63" s="186" t="n">
-        <v>0.0002302220548744464</v>
+        <v>0.0002302220548744465</v>
       </c>
       <c r="X63" s="187" t="n">
         <v>0</v>
       </c>
       <c r="Y63" s="185" t="n">
-        <v>0.007712308276091395</v>
+        <v>0.007712308276091856</v>
       </c>
       <c r="Z63" s="186" t="n">
-        <v>0.006956584238285445</v>
+        <v>0.006956584238285447</v>
       </c>
       <c r="AA63" s="186" t="n">
         <v>0.006344609675263325</v>
@@ -7026,7 +7026,7 @@
         <v>0</v>
       </c>
       <c r="AD63" s="188" t="n">
-        <v>1042.851247240796</v>
+        <v>1042.851247240795</v>
       </c>
       <c r="AE63" s="189" t="n">
         <v>1026.036120231115</v>
@@ -7035,7 +7035,7 @@
         <v>1010.654642836487</v>
       </c>
       <c r="AG63" s="189" t="n">
-        <v>39.44645797619314</v>
+        <v>39.44645797619315</v>
       </c>
       <c r="AH63" s="190" t="n">
         <v>0</v>
@@ -7300,46 +7300,46 @@
         <v>0.004145782646036412</v>
       </c>
       <c r="D68" s="149" t="n">
-        <v>0.005862050084171071</v>
+        <v>0.005862050084171073</v>
       </c>
       <c r="E68" s="149" t="n">
         <v>0.007609732210569715</v>
       </c>
       <c r="F68" s="149" t="n">
-        <v>0.009245243871474511</v>
+        <v>0.009245243871474509</v>
       </c>
       <c r="G68" s="150" t="n">
-        <v>0.01065056201700851</v>
+        <v>0.0106505620170085</v>
       </c>
       <c r="H68" s="148" t="n">
-        <v>0.004107078251164723</v>
+        <v>0.004107078251165104</v>
       </c>
       <c r="I68" s="149" t="n">
-        <v>0.005822146131905999</v>
+        <v>0.005822146131906001</v>
       </c>
       <c r="J68" s="149" t="n">
         <v>0.007574820478380469</v>
       </c>
       <c r="K68" s="149" t="n">
-        <v>0.009221791357426042</v>
+        <v>0.00922179135742604</v>
       </c>
       <c r="L68" s="150" t="n">
-        <v>0.01064602120713725</v>
+        <v>0.01064602120713724</v>
       </c>
       <c r="M68" s="151" t="n">
-        <v>442.6297812764453</v>
+        <v>442.6297812764452</v>
       </c>
       <c r="N68" s="152" t="n">
-        <v>687.7416751552466</v>
+        <v>687.741675155247</v>
       </c>
       <c r="O68" s="152" t="n">
-        <v>968.0315152083137</v>
+        <v>968.0315152083139</v>
       </c>
       <c r="P68" s="152" t="n">
         <v>1269.203770234304</v>
       </c>
       <c r="Q68" s="153" t="n">
-        <v>1618.820227011515</v>
+        <v>1618.820227011514</v>
       </c>
       <c r="S68" s="21" t="inlineStr">
         <is>
@@ -7350,46 +7350,46 @@
         <v>0.004288309673544728</v>
       </c>
       <c r="U68" s="149" t="n">
-        <v>0.006063580324643411</v>
+        <v>0.006063580324643413</v>
       </c>
       <c r="V68" s="149" t="n">
         <v>0.007871345663253664</v>
       </c>
       <c r="W68" s="149" t="n">
-        <v>0.009563084250504153</v>
+        <v>0.009563084250504152</v>
       </c>
       <c r="X68" s="150" t="n">
-        <v>0.01101671554583098</v>
+        <v>0.01101671554583097</v>
       </c>
       <c r="Y68" s="148" t="n">
-        <v>0.004254890974917172</v>
+        <v>0.004254890974917501</v>
       </c>
       <c r="Z68" s="149" t="n">
-        <v>0.006029140415107905</v>
+        <v>0.006029140415107908</v>
       </c>
       <c r="AA68" s="149" t="n">
         <v>0.007841225536757432</v>
       </c>
       <c r="AB68" s="149" t="n">
-        <v>0.009542857489453797</v>
+        <v>0.009542857489453795</v>
       </c>
       <c r="AC68" s="150" t="n">
-        <v>0.01101280067386949</v>
+        <v>0.01101280067386948</v>
       </c>
       <c r="AD68" s="151" t="n">
-        <v>442.6297812764453</v>
+        <v>442.6297812764452</v>
       </c>
       <c r="AE68" s="152" t="n">
-        <v>687.7416751552466</v>
+        <v>687.741675155247</v>
       </c>
       <c r="AF68" s="152" t="n">
-        <v>968.0315152083137</v>
+        <v>968.0315152083139</v>
       </c>
       <c r="AG68" s="152" t="n">
         <v>1269.203770234304</v>
       </c>
       <c r="AH68" s="153" t="n">
-        <v>1618.820227011515</v>
+        <v>1618.820227011514</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" thickBot="1">
@@ -7504,46 +7504,46 @@
         <v>0.003414366568563665</v>
       </c>
       <c r="D70" s="162" t="n">
-        <v>0.004850955558179512</v>
+        <v>0.004850955558179513</v>
       </c>
       <c r="E70" s="162" t="n">
         <v>0.006311039074502522</v>
       </c>
       <c r="F70" s="162" t="n">
-        <v>0.007674304579271227</v>
+        <v>0.007674304579271225</v>
       </c>
       <c r="G70" s="163" t="n">
-        <v>0.008849528788739899</v>
+        <v>0.00884952878873989</v>
       </c>
       <c r="H70" s="161" t="n">
-        <v>0.003381906077886425</v>
+        <v>0.003381906077886683</v>
       </c>
       <c r="I70" s="162" t="n">
-        <v>0.004816970390101331</v>
+        <v>0.004816970390101332</v>
       </c>
       <c r="J70" s="162" t="n">
-        <v>0.006280849655582268</v>
+        <v>0.006280849655582267</v>
       </c>
       <c r="K70" s="162" t="n">
-        <v>0.007653447546955522</v>
+        <v>0.00765344754695552</v>
       </c>
       <c r="L70" s="163" t="n">
-        <v>0.008844306853956168</v>
+        <v>0.008844306853956159</v>
       </c>
       <c r="M70" s="164" t="n">
-        <v>442.6297812764453</v>
+        <v>442.6297812764452</v>
       </c>
       <c r="N70" s="165" t="n">
-        <v>687.7416751552466</v>
+        <v>687.741675155247</v>
       </c>
       <c r="O70" s="165" t="n">
-        <v>968.0315152083137</v>
+        <v>968.0315152083139</v>
       </c>
       <c r="P70" s="165" t="n">
         <v>1269.203770234304</v>
       </c>
       <c r="Q70" s="166" t="n">
-        <v>1618.820227011515</v>
+        <v>1618.820227011514</v>
       </c>
       <c r="S70" s="42" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>0.003518189184143019</v>
       </c>
       <c r="U70" s="162" t="n">
-        <v>0.004998890266676356</v>
+        <v>0.004998890266676359</v>
       </c>
       <c r="V70" s="162" t="n">
         <v>0.006503757982568754</v>
@@ -7563,13 +7563,13 @@
         <v>0.007908781222228531</v>
       </c>
       <c r="X70" s="163" t="n">
-        <v>0.009120074673714616</v>
+        <v>0.009120074673714607</v>
       </c>
       <c r="Y70" s="161" t="n">
-        <v>0.003489124490867706</v>
+        <v>0.003489124490867928</v>
       </c>
       <c r="Z70" s="162" t="n">
-        <v>0.004968432924001936</v>
+        <v>0.004968432924001938</v>
       </c>
       <c r="AA70" s="162" t="n">
         <v>0.006476655361335768</v>
@@ -7578,22 +7578,22 @@
         <v>0.007889974302879878</v>
       </c>
       <c r="AC70" s="163" t="n">
-        <v>0.009115182625554214</v>
+        <v>0.009115182625554207</v>
       </c>
       <c r="AD70" s="164" t="n">
-        <v>442.6297812764453</v>
+        <v>442.6297812764452</v>
       </c>
       <c r="AE70" s="165" t="n">
-        <v>687.7416751552466</v>
+        <v>687.741675155247</v>
       </c>
       <c r="AF70" s="165" t="n">
-        <v>968.0315152083137</v>
+        <v>968.0315152083139</v>
       </c>
       <c r="AG70" s="165" t="n">
         <v>1269.203770234304</v>
       </c>
       <c r="AH70" s="166" t="n">
-        <v>1618.820227011515</v>
+        <v>1618.820227011514</v>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" thickBot="1">
@@ -7603,46 +7603,46 @@
         </is>
       </c>
       <c r="C71" s="155" t="n">
-        <v>0.00914674448939419</v>
+        <v>0.009146744489394185</v>
       </c>
       <c r="D71" s="156" t="n">
-        <v>0.01304912885657689</v>
+        <v>0.0130491288565769</v>
       </c>
       <c r="E71" s="156" t="n">
         <v>0.01686236857256706</v>
       </c>
       <c r="F71" s="156" t="n">
-        <v>0.02019242424038005</v>
+        <v>0.02019242424038006</v>
       </c>
       <c r="G71" s="157" t="n">
-        <v>0.02292483464809903</v>
+        <v>0.02292483464809904</v>
       </c>
       <c r="H71" s="155" t="n">
-        <v>0.009103628998697324</v>
+        <v>0.009103628998697318</v>
       </c>
       <c r="I71" s="156" t="n">
-        <v>0.01301240649175741</v>
+        <v>0.01301240649175742</v>
       </c>
       <c r="J71" s="156" t="n">
         <v>0.01684523311266995</v>
       </c>
       <c r="K71" s="156" t="n">
-        <v>0.02019242424038005</v>
+        <v>0.02019242424038006</v>
       </c>
       <c r="L71" s="157" t="n">
-        <v>0.02292483464809903</v>
+        <v>0.02292483464809904</v>
       </c>
       <c r="M71" s="158" t="n">
-        <v>74.01349205344737</v>
+        <v>74.01349205344734</v>
       </c>
       <c r="N71" s="159" t="n">
-        <v>115.3857395590852</v>
+        <v>115.3857395590853</v>
       </c>
       <c r="O71" s="159" t="n">
         <v>163.146278276518</v>
       </c>
       <c r="P71" s="159" t="n">
-        <v>214.9713475067102</v>
+        <v>214.9713475067103</v>
       </c>
       <c r="Q71" s="160" t="n">
         <v>276.4336872430843</v>
@@ -7653,46 +7653,46 @@
         </is>
       </c>
       <c r="T71" s="155" t="n">
-        <v>0.0112184593810647</v>
+        <v>0.01121845938106469</v>
       </c>
       <c r="U71" s="156" t="n">
-        <v>0.01600472410763525</v>
+        <v>0.01600472410763526</v>
       </c>
       <c r="V71" s="156" t="n">
         <v>0.02068165314109639</v>
       </c>
       <c r="W71" s="156" t="n">
-        <v>0.02476595814047204</v>
+        <v>0.02476595814047205</v>
       </c>
       <c r="X71" s="157" t="n">
-        <v>0.02811725271385135</v>
+        <v>0.02811725271385136</v>
       </c>
       <c r="Y71" s="155" t="n">
-        <v>0.01116123031988268</v>
+        <v>0.01116123031988267</v>
       </c>
       <c r="Z71" s="156" t="n">
-        <v>0.01595597326934485</v>
+        <v>0.01595597326934487</v>
       </c>
       <c r="AA71" s="156" t="n">
         <v>0.02065890155206251</v>
       </c>
       <c r="AB71" s="156" t="n">
-        <v>0.02476595814047204</v>
+        <v>0.02476595814047205</v>
       </c>
       <c r="AC71" s="157" t="n">
-        <v>0.02811725271385135</v>
+        <v>0.02811725271385136</v>
       </c>
       <c r="AD71" s="158" t="n">
-        <v>74.01349205344737</v>
+        <v>74.01349205344734</v>
       </c>
       <c r="AE71" s="159" t="n">
-        <v>115.3857395590852</v>
+        <v>115.3857395590853</v>
       </c>
       <c r="AF71" s="159" t="n">
         <v>163.146278276518</v>
       </c>
       <c r="AG71" s="159" t="n">
-        <v>214.9713475067102</v>
+        <v>214.9713475067103</v>
       </c>
       <c r="AH71" s="160" t="n">
         <v>276.4336872430843</v>
@@ -7708,37 +7708,37 @@
         <v>0.003751151786175461</v>
       </c>
       <c r="D72" s="162" t="n">
-        <v>0.005332253555395017</v>
+        <v>0.005332253555395019</v>
       </c>
       <c r="E72" s="162" t="n">
-        <v>0.006937094080221839</v>
+        <v>0.006937094080221838</v>
       </c>
       <c r="F72" s="162" t="n">
-        <v>0.008431390697727303</v>
+        <v>0.008431390697727302</v>
       </c>
       <c r="G72" s="163" t="n">
-        <v>0.00971997148234119</v>
+        <v>0.009719971482341183</v>
       </c>
       <c r="H72" s="161" t="n">
-        <v>0.003716541046652751</v>
+        <v>0.003716541046653017</v>
       </c>
       <c r="I72" s="162" t="n">
-        <v>0.005296203478792829</v>
+        <v>0.005296203478792831</v>
       </c>
       <c r="J72" s="162" t="n">
-        <v>0.006905455055277996</v>
+        <v>0.006905455055277995</v>
       </c>
       <c r="K72" s="162" t="n">
-        <v>0.008409858394997922</v>
+        <v>0.008409858394997921</v>
       </c>
       <c r="L72" s="163" t="n">
-        <v>0.009714590417804619</v>
+        <v>0.009714590417804612</v>
       </c>
       <c r="M72" s="164" t="n">
-        <v>516.6432733298926</v>
+        <v>516.6432733298925</v>
       </c>
       <c r="N72" s="165" t="n">
-        <v>803.1274147143318</v>
+        <v>803.1274147143323</v>
       </c>
       <c r="O72" s="165" t="n">
         <v>1131.177793484832</v>
@@ -7747,7 +7747,7 @@
         <v>1484.175117741015</v>
       </c>
       <c r="Q72" s="166" t="n">
-        <v>1895.253914254599</v>
+        <v>1895.253914254598</v>
       </c>
       <c r="S72" s="42" t="inlineStr">
         <is>
@@ -7758,37 +7758,37 @@
         <v>0.003901865661019058</v>
       </c>
       <c r="U72" s="162" t="n">
-        <v>0.005546906316535389</v>
+        <v>0.005546906316535392</v>
       </c>
       <c r="V72" s="162" t="n">
-        <v>0.007217351083230759</v>
+        <v>0.007217351083230757</v>
       </c>
       <c r="W72" s="162" t="n">
         <v>0.00877377202185586</v>
       </c>
       <c r="X72" s="163" t="n">
-        <v>0.01011707357930958</v>
+        <v>0.01011707357930957</v>
       </c>
       <c r="Y72" s="161" t="n">
-        <v>0.00387024380166505</v>
+        <v>0.003870243801665283</v>
       </c>
       <c r="Z72" s="162" t="n">
-        <v>0.005513949085470351</v>
+        <v>0.005513949085470355</v>
       </c>
       <c r="AA72" s="162" t="n">
-        <v>0.007188385676528911</v>
+        <v>0.00718838567652891</v>
       </c>
       <c r="AB72" s="162" t="n">
         <v>0.00875397634149701</v>
       </c>
       <c r="AC72" s="163" t="n">
-        <v>0.01011193140021456</v>
+        <v>0.01011193140021455</v>
       </c>
       <c r="AD72" s="164" t="n">
-        <v>516.6432733298926</v>
+        <v>516.6432733298925</v>
       </c>
       <c r="AE72" s="165" t="n">
-        <v>803.1274147143318</v>
+        <v>803.1274147143323</v>
       </c>
       <c r="AF72" s="165" t="n">
         <v>1131.177793484832</v>
@@ -7797,7 +7797,7 @@
         <v>1484.175117741015</v>
       </c>
       <c r="AH72" s="166" t="n">
-        <v>1895.253914254599</v>
+        <v>1895.253914254598</v>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1" thickBot="1">
@@ -7909,40 +7909,40 @@
         </is>
       </c>
       <c r="C74" s="179" t="n">
-        <v>0.00371328053204457</v>
+        <v>0.003713280532044571</v>
       </c>
       <c r="D74" s="180" t="n">
-        <v>0.005279884317447909</v>
+        <v>0.005279884317447911</v>
       </c>
       <c r="E74" s="180" t="n">
         <v>0.006870924865320174</v>
       </c>
       <c r="F74" s="180" t="n">
-        <v>0.008347211466634582</v>
+        <v>0.00834721146663458</v>
       </c>
       <c r="G74" s="181" t="n">
-        <v>0.009621979873623388</v>
+        <v>0.009621979873623381</v>
       </c>
       <c r="H74" s="179" t="n">
-        <v>0.00367930526381215</v>
+        <v>0.003679305263812411</v>
       </c>
       <c r="I74" s="180" t="n">
-        <v>0.005244460503149989</v>
+        <v>0.005244460503149991</v>
       </c>
       <c r="J74" s="180" t="n">
-        <v>0.006839790586017091</v>
+        <v>0.006839790586017089</v>
       </c>
       <c r="K74" s="180" t="n">
-        <v>0.008325997432609708</v>
+        <v>0.008325997432609707</v>
       </c>
       <c r="L74" s="181" t="n">
-        <v>0.00961659054511318</v>
+        <v>0.009616590545113173</v>
       </c>
       <c r="M74" s="182" t="n">
-        <v>516.6432733298926</v>
+        <v>516.6432733298925</v>
       </c>
       <c r="N74" s="183" t="n">
-        <v>803.1274147143318</v>
+        <v>803.1274147143323</v>
       </c>
       <c r="O74" s="183" t="n">
         <v>1131.177793484832</v>
@@ -7951,7 +7951,7 @@
         <v>1484.175117741015</v>
       </c>
       <c r="Q74" s="184" t="n">
-        <v>1895.253914254599</v>
+        <v>1895.253914254598</v>
       </c>
       <c r="S74" s="51" t="inlineStr">
         <is>
@@ -7959,40 +7959,40 @@
         </is>
       </c>
       <c r="T74" s="185" t="n">
-        <v>0.003851676283334987</v>
+        <v>0.003851676283334988</v>
       </c>
       <c r="U74" s="186" t="n">
-        <v>0.005477487735988124</v>
+        <v>0.005477487735988128</v>
       </c>
       <c r="V74" s="186" t="n">
-        <v>0.007129608754350134</v>
+        <v>0.007129608754350133</v>
       </c>
       <c r="W74" s="186" t="n">
-        <v>0.008662117283282512</v>
+        <v>0.008662117283282511</v>
       </c>
       <c r="X74" s="187" t="n">
-        <v>0.009987040572517007</v>
+        <v>0.009987040572517</v>
       </c>
       <c r="Y74" s="185" t="n">
-        <v>0.003820786716448209</v>
+        <v>0.003820786716448438</v>
       </c>
       <c r="Z74" s="186" t="n">
-        <v>0.005445250322452764</v>
+        <v>0.005445250322452766</v>
       </c>
       <c r="AA74" s="186" t="n">
-        <v>0.007101220603750817</v>
+        <v>0.007101220603750816</v>
       </c>
       <c r="AB74" s="186" t="n">
-        <v>0.008642681896762313</v>
+        <v>0.008642681896762311</v>
       </c>
       <c r="AC74" s="187" t="n">
-        <v>0.009981880715822324</v>
+        <v>0.009981880715822317</v>
       </c>
       <c r="AD74" s="188" t="n">
-        <v>516.6432733298926</v>
+        <v>516.6432733298925</v>
       </c>
       <c r="AE74" s="189" t="n">
-        <v>803.1274147143318</v>
+        <v>803.1274147143323</v>
       </c>
       <c r="AF74" s="189" t="n">
         <v>1131.177793484832</v>
@@ -8001,7 +8001,7 @@
         <v>1484.175117741015</v>
       </c>
       <c r="AH74" s="190" t="n">
-        <v>1895.253914254599</v>
+        <v>1895.253914254598</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1" thickBot="1"/>
@@ -8260,40 +8260,40 @@
         </is>
       </c>
       <c r="C79" s="148" t="n">
-        <v>466.6960857993933</v>
+        <v>466.6960857993934</v>
       </c>
       <c r="D79" s="149" t="n">
-        <v>503.0285132179619</v>
+        <v>503.0285132179617</v>
       </c>
       <c r="E79" s="149" t="n">
         <v>538.7660517631344</v>
       </c>
       <c r="F79" s="149" t="n">
-        <v>575.9169426275228</v>
+        <v>575.9169426275226</v>
       </c>
       <c r="G79" s="150" t="n">
         <v>606.7737387263293</v>
       </c>
       <c r="H79" s="148" t="n">
-        <v>462.3390822774839</v>
+        <v>462.3390822775268</v>
       </c>
       <c r="I79" s="149" t="n">
-        <v>499.6043142617602</v>
+        <v>499.6043142617601</v>
       </c>
       <c r="J79" s="149" t="n">
-        <v>536.2943148358238</v>
+        <v>536.2943148358237</v>
       </c>
       <c r="K79" s="149" t="n">
-        <v>574.4560076456563</v>
+        <v>574.4560076456562</v>
       </c>
       <c r="L79" s="150" t="n">
         <v>606.515044004114</v>
       </c>
       <c r="M79" s="151" t="n">
-        <v>49827403.89862307</v>
+        <v>49827403.89862306</v>
       </c>
       <c r="N79" s="152" t="n">
-        <v>59015816.54266847</v>
+        <v>59015816.54266845</v>
       </c>
       <c r="O79" s="152" t="n">
         <v>68536251.07946102</v>
@@ -8313,37 +8313,37 @@
         <v>482.7405366396579</v>
       </c>
       <c r="U79" s="149" t="n">
-        <v>520.322029270818</v>
+        <v>520.3220292708178</v>
       </c>
       <c r="V79" s="149" t="n">
-        <v>557.2881814636881</v>
+        <v>557.288181463688</v>
       </c>
       <c r="W79" s="149" t="n">
-        <v>595.7162753308072</v>
+        <v>595.7162753308071</v>
       </c>
       <c r="X79" s="150" t="n">
         <v>627.6338910146919</v>
       </c>
       <c r="Y79" s="148" t="n">
-        <v>478.9785507437257</v>
+        <v>478.9785507437627</v>
       </c>
       <c r="Z79" s="149" t="n">
-        <v>517.3667054096682</v>
+        <v>517.3667054096679</v>
       </c>
       <c r="AA79" s="149" t="n">
-        <v>555.1556883375251</v>
+        <v>555.155688337525</v>
       </c>
       <c r="AB79" s="149" t="n">
-        <v>594.4562832153671</v>
+        <v>594.456283215367</v>
       </c>
       <c r="AC79" s="150" t="n">
         <v>627.4108566346367</v>
       </c>
       <c r="AD79" s="151" t="n">
-        <v>49827403.89862307</v>
+        <v>49827403.89862306</v>
       </c>
       <c r="AE79" s="152" t="n">
-        <v>59015816.54266847</v>
+        <v>59015816.54266845</v>
       </c>
       <c r="AF79" s="152" t="n">
         <v>68536251.07946102</v>
@@ -8401,7 +8401,7 @@
         <v>26918786.74444624</v>
       </c>
       <c r="P80" s="159" t="n">
-        <v>30441440.5802585</v>
+        <v>30441440.58025851</v>
       </c>
       <c r="Q80" s="160" t="n">
         <v>34884383.99516487</v>
@@ -8418,7 +8418,7 @@
         <v>983.0906839097471</v>
       </c>
       <c r="V80" s="156" t="n">
-        <v>1040.936319718563</v>
+        <v>1040.936319718564</v>
       </c>
       <c r="W80" s="156" t="n">
         <v>1096.544665140292</v>
@@ -8436,7 +8436,7 @@
         <v>1034.915386898416</v>
       </c>
       <c r="AB80" s="156" t="n">
-        <v>1092.561046000476</v>
+        <v>1092.561046000477</v>
       </c>
       <c r="AC80" s="157" t="n">
         <v>1139.952583001598</v>
@@ -8451,7 +8451,7 @@
         <v>26918786.74444624</v>
       </c>
       <c r="AG80" s="159" t="n">
-        <v>30441440.5802585</v>
+        <v>30441440.58025851</v>
       </c>
       <c r="AH80" s="160" t="n">
         <v>34884383.99516487</v>
@@ -8464,13 +8464,13 @@
         </is>
       </c>
       <c r="C81" s="161" t="n">
-        <v>545.302013049922</v>
+        <v>545.3020130499223</v>
       </c>
       <c r="D81" s="162" t="n">
-        <v>583.7756884895231</v>
+        <v>583.7756884895228</v>
       </c>
       <c r="E81" s="162" t="n">
-        <v>622.3149392353804</v>
+        <v>622.3149392353803</v>
       </c>
       <c r="F81" s="162" t="n">
         <v>662.1236223647419</v>
@@ -8479,10 +8479,10 @@
         <v>694.8678079911892</v>
       </c>
       <c r="H81" s="161" t="n">
-        <v>540.1178096097117</v>
+        <v>540.117809609753</v>
       </c>
       <c r="I81" s="162" t="n">
-        <v>579.6858314179984</v>
+        <v>579.6858314179982</v>
       </c>
       <c r="J81" s="162" t="n">
         <v>619.3380401575703</v>
@@ -8497,10 +8497,10 @@
         <v>70691563.40393442</v>
       </c>
       <c r="N81" s="165" t="n">
-        <v>82764491.47008137</v>
+        <v>82764491.47008136</v>
       </c>
       <c r="O81" s="165" t="n">
-        <v>95455037.82390726</v>
+        <v>95455037.82390727</v>
       </c>
       <c r="P81" s="165" t="n">
         <v>109504358.2367601</v>
@@ -8514,31 +8514,31 @@
         </is>
       </c>
       <c r="T81" s="161" t="n">
-        <v>561.8833261979554</v>
+        <v>561.8833261979555</v>
       </c>
       <c r="U81" s="162" t="n">
-        <v>601.5785080100244</v>
+        <v>601.5785080100243</v>
       </c>
       <c r="V81" s="162" t="n">
-        <v>641.3184431191207</v>
+        <v>641.3184431191206</v>
       </c>
       <c r="W81" s="162" t="n">
-        <v>682.3537973064767</v>
+        <v>682.3537973064768</v>
       </c>
       <c r="X81" s="163" t="n">
         <v>716.111156709668</v>
       </c>
       <c r="Y81" s="161" t="n">
-        <v>557.2414591243875</v>
+        <v>557.2414591244229</v>
       </c>
       <c r="Z81" s="162" t="n">
-        <v>597.9131979538765</v>
+        <v>597.9131979538764</v>
       </c>
       <c r="AA81" s="162" t="n">
         <v>638.6459250303217</v>
       </c>
       <c r="AB81" s="162" t="n">
-        <v>680.7311739878394</v>
+        <v>680.7311739878395</v>
       </c>
       <c r="AC81" s="163" t="n">
         <v>715.7270315361186</v>
@@ -8547,10 +8547,10 @@
         <v>70691563.40393442</v>
       </c>
       <c r="AE81" s="165" t="n">
-        <v>82764491.47008137</v>
+        <v>82764491.47008136</v>
       </c>
       <c r="AF81" s="165" t="n">
-        <v>95455037.82390726</v>
+        <v>95455037.82390727</v>
       </c>
       <c r="AG81" s="165" t="n">
         <v>109504358.2367601</v>
@@ -8566,13 +8566,13 @@
         </is>
       </c>
       <c r="C82" s="155" t="n">
-        <v>874.3488589583443</v>
+        <v>874.3488589583444</v>
       </c>
       <c r="D82" s="156" t="n">
         <v>927.6263505918112</v>
       </c>
       <c r="E82" s="156" t="n">
-        <v>971.1213793260646</v>
+        <v>971.1213793260649</v>
       </c>
       <c r="F82" s="156" t="n">
         <v>1013.652199235176</v>
@@ -8587,7 +8587,7 @@
         <v>925.0158596052482</v>
       </c>
       <c r="J82" s="156" t="n">
-        <v>970.1345303327543</v>
+        <v>970.1345303327546</v>
       </c>
       <c r="K82" s="156" t="n">
         <v>1013.652199235176</v>
@@ -8596,13 +8596,13 @@
         <v>1039.373711732196</v>
       </c>
       <c r="M82" s="158" t="n">
-        <v>7075043.191541074</v>
+        <v>7075043.191541075</v>
       </c>
       <c r="N82" s="159" t="n">
         <v>8202451.954759018</v>
       </c>
       <c r="O82" s="159" t="n">
-        <v>9395764.189946579</v>
+        <v>9395764.189946583</v>
       </c>
       <c r="P82" s="159" t="n">
         <v>10791481.82400831</v>
@@ -8622,7 +8622,7 @@
         <v>1137.731413289841</v>
       </c>
       <c r="V82" s="156" t="n">
-        <v>1191.07795792102</v>
+        <v>1191.077957921021</v>
       </c>
       <c r="W82" s="156" t="n">
         <v>1243.241902824804</v>
@@ -8637,7 +8637,7 @@
         <v>1134.26585151107</v>
       </c>
       <c r="AA82" s="156" t="n">
-        <v>1189.767670197836</v>
+        <v>1189.767670197837</v>
       </c>
       <c r="AB82" s="156" t="n">
         <v>1243.241902824804</v>
@@ -8646,13 +8646,13 @@
         <v>1274.789273968926</v>
       </c>
       <c r="AD82" s="158" t="n">
-        <v>7075043.191541074</v>
+        <v>7075043.191541075</v>
       </c>
       <c r="AE82" s="159" t="n">
         <v>8202451.954759018</v>
       </c>
       <c r="AF82" s="159" t="n">
-        <v>9395764.189946579</v>
+        <v>9395764.189946583</v>
       </c>
       <c r="AG82" s="159" t="n">
         <v>10791481.82400831</v>
@@ -8668,10 +8668,10 @@
         </is>
       </c>
       <c r="C83" s="161" t="n">
-        <v>564.6339753061175</v>
+        <v>564.6339753061176</v>
       </c>
       <c r="D83" s="162" t="n">
-        <v>603.9624580279773</v>
+        <v>603.962458027977</v>
       </c>
       <c r="E83" s="162" t="n">
         <v>643.0111005945687</v>
@@ -8683,10 +8683,10 @@
         <v>716.172684049316</v>
       </c>
       <c r="H83" s="161" t="n">
-        <v>559.4242689122002</v>
+        <v>559.4242689122404</v>
       </c>
       <c r="I83" s="162" t="n">
-        <v>599.8792139266676</v>
+        <v>599.8792139266674</v>
       </c>
       <c r="J83" s="162" t="n">
         <v>640.0784253251238</v>
@@ -8701,13 +8701,13 @@
         <v>77766606.59547549</v>
       </c>
       <c r="N83" s="165" t="n">
-        <v>90966943.42484039</v>
+        <v>90966943.42484038</v>
       </c>
       <c r="O83" s="165" t="n">
         <v>104850802.0138538</v>
       </c>
       <c r="P83" s="165" t="n">
-        <v>120295840.0607684</v>
+        <v>120295840.0607685</v>
       </c>
       <c r="Q83" s="166" t="n">
         <v>139643319.4472456</v>
@@ -8718,31 +8718,31 @@
         </is>
       </c>
       <c r="T83" s="161" t="n">
-        <v>587.3198539741976</v>
+        <v>587.3198539741977</v>
       </c>
       <c r="U83" s="162" t="n">
-        <v>628.2752945977354</v>
+        <v>628.2752945977353</v>
       </c>
       <c r="V83" s="162" t="n">
         <v>668.9886009528077</v>
       </c>
       <c r="W83" s="162" t="n">
-        <v>711.1345981040701</v>
+        <v>711.1345981040703</v>
       </c>
       <c r="X83" s="163" t="n">
         <v>745.431378392621</v>
       </c>
       <c r="Y83" s="161" t="n">
-        <v>582.5600422759809</v>
+        <v>582.5600422760161</v>
       </c>
       <c r="Z83" s="162" t="n">
-        <v>624.5423644065788</v>
+        <v>624.5423644065787</v>
       </c>
       <c r="AA83" s="162" t="n">
         <v>666.3037479254248</v>
       </c>
       <c r="AB83" s="162" t="n">
-        <v>709.53011223857</v>
+        <v>709.5301122385703</v>
       </c>
       <c r="AC83" s="163" t="n">
         <v>745.0524998937454</v>
@@ -8751,13 +8751,13 @@
         <v>77766606.59547549</v>
       </c>
       <c r="AE83" s="165" t="n">
-        <v>90966943.42484039</v>
+        <v>90966943.42484038</v>
       </c>
       <c r="AF83" s="165" t="n">
         <v>104850802.0138538</v>
       </c>
       <c r="AG83" s="165" t="n">
-        <v>120295840.0607684</v>
+        <v>120295840.0607685</v>
       </c>
       <c r="AH83" s="166" t="n">
         <v>139643319.4472456</v>
@@ -8770,49 +8770,49 @@
         </is>
       </c>
       <c r="C84" s="155" t="n">
-        <v>4903.09882097024</v>
+        <v>4903.098820970239</v>
       </c>
       <c r="D84" s="156" t="n">
-        <v>5104.15033982229</v>
+        <v>5104.150339822286</v>
       </c>
       <c r="E84" s="156" t="n">
-        <v>5701.495554346445</v>
+        <v>5701.495554346443</v>
       </c>
       <c r="F84" s="156" t="n">
-        <v>5996.951367971826</v>
+        <v>5996.951367971824</v>
       </c>
       <c r="G84" s="157" t="n">
-        <v>6396.604666196193</v>
+        <v>6396.604666196188</v>
       </c>
       <c r="H84" s="155" t="n">
-        <v>4895.558019140843</v>
+        <v>4895.558019140841</v>
       </c>
       <c r="I84" s="156" t="n">
-        <v>5096.577036070787</v>
+        <v>5096.577036070783</v>
       </c>
       <c r="J84" s="156" t="n">
-        <v>5693.202843680533</v>
+        <v>5693.202843680531</v>
       </c>
       <c r="K84" s="156" t="n">
-        <v>5989.077941201233</v>
+        <v>5989.077941201232</v>
       </c>
       <c r="L84" s="157" t="n">
-        <v>6388.94385274572</v>
+        <v>6388.943852745716</v>
       </c>
       <c r="M84" s="158" t="n">
-        <v>6887295.46461808</v>
+        <v>6887295.464618078</v>
       </c>
       <c r="N84" s="159" t="n">
-        <v>7625160.038233255</v>
+        <v>7625160.038233248</v>
       </c>
       <c r="O84" s="159" t="n">
-        <v>8953294.267540315</v>
+        <v>8953294.267540311</v>
       </c>
       <c r="P84" s="159" t="n">
         <v>10645841.53973097</v>
       </c>
       <c r="Q84" s="160" t="n">
-        <v>12702124.50693289</v>
+        <v>12702124.50693288</v>
       </c>
       <c r="S84" s="32" t="inlineStr">
         <is>
@@ -8820,49 +8820,49 @@
         </is>
       </c>
       <c r="T84" s="155" t="n">
-        <v>3991.794880193408</v>
+        <v>3991.794880193406</v>
       </c>
       <c r="U84" s="156" t="n">
-        <v>4155.478389931421</v>
+        <v>4155.478389931416</v>
       </c>
       <c r="V84" s="156" t="n">
-        <v>4641.799318003946</v>
+        <v>4641.799318003944</v>
       </c>
       <c r="W84" s="156" t="n">
-        <v>4882.340870849865</v>
+        <v>4882.340870849863</v>
       </c>
       <c r="X84" s="157" t="n">
-        <v>5207.713466417649</v>
+        <v>5207.713466417646</v>
       </c>
       <c r="Y84" s="155" t="n">
         <v>3985.8462016986</v>
       </c>
       <c r="Z84" s="156" t="n">
-        <v>4149.504081860304</v>
+        <v>4149.5040818603</v>
       </c>
       <c r="AA84" s="156" t="n">
-        <v>4635.257501539254</v>
+        <v>4635.257501539252</v>
       </c>
       <c r="AB84" s="156" t="n">
-        <v>4876.129839468537</v>
+        <v>4876.129839468535</v>
       </c>
       <c r="AC84" s="157" t="n">
-        <v>5201.670178834523</v>
+        <v>5201.67017883452</v>
       </c>
       <c r="AD84" s="158" t="n">
-        <v>6887295.46461808</v>
+        <v>6887295.464618078</v>
       </c>
       <c r="AE84" s="159" t="n">
-        <v>7625160.038233255</v>
+        <v>7625160.038233248</v>
       </c>
       <c r="AF84" s="159" t="n">
-        <v>8953294.267540315</v>
+        <v>8953294.267540311</v>
       </c>
       <c r="AG84" s="159" t="n">
         <v>10645841.53973097</v>
       </c>
       <c r="AH84" s="160" t="n">
-        <v>12702124.50693289</v>
+        <v>12702124.50693288</v>
       </c>
     </row>
     <row r="85" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -8872,13 +8872,13 @@
         </is>
       </c>
       <c r="C85" s="179" t="n">
-        <v>608.4346834815656</v>
+        <v>608.4346834815657</v>
       </c>
       <c r="D85" s="180" t="n">
-        <v>648.1597955214152</v>
+        <v>648.159795521415</v>
       </c>
       <c r="E85" s="180" t="n">
-        <v>691.2612671666698</v>
+        <v>691.2612671666695</v>
       </c>
       <c r="F85" s="180" t="n">
         <v>736.4345979467018</v>
@@ -8887,13 +8887,13 @@
         <v>773.4397932331132</v>
       </c>
       <c r="H85" s="179" t="n">
-        <v>602.8677107212792</v>
+        <v>602.8677107213221</v>
       </c>
       <c r="I85" s="180" t="n">
-        <v>643.8111600492225</v>
+        <v>643.8111600492223</v>
       </c>
       <c r="J85" s="180" t="n">
-        <v>688.1289492058083</v>
+        <v>688.1289492058082</v>
       </c>
       <c r="K85" s="180" t="n">
         <v>734.5629850517389</v>
@@ -8902,10 +8902,10 @@
         <v>773.0065849762525</v>
       </c>
       <c r="M85" s="182" t="n">
-        <v>84653902.06009358</v>
+        <v>84653902.06009357</v>
       </c>
       <c r="N85" s="183" t="n">
-        <v>98592103.46307364</v>
+        <v>98592103.46307363</v>
       </c>
       <c r="O85" s="183" t="n">
         <v>113804096.2813942</v>
@@ -8922,13 +8922,13 @@
         </is>
       </c>
       <c r="T85" s="185" t="n">
-        <v>631.1113367548411</v>
+        <v>631.1113367548412</v>
       </c>
       <c r="U85" s="186" t="n">
-        <v>672.4176359691899</v>
+        <v>672.4176359691897</v>
       </c>
       <c r="V85" s="186" t="n">
-        <v>717.2866067579969</v>
+        <v>717.2866067579968</v>
       </c>
       <c r="W85" s="186" t="n">
         <v>764.2172340283653</v>
@@ -8937,13 +8937,13 @@
         <v>802.784322652035</v>
       </c>
       <c r="Y85" s="185" t="n">
-        <v>626.0499675182725</v>
+        <v>626.04996751831</v>
       </c>
       <c r="Z85" s="186" t="n">
-        <v>668.460163776822</v>
+        <v>668.4601637768219</v>
       </c>
       <c r="AA85" s="186" t="n">
-        <v>714.4305678199423</v>
+        <v>714.4305678199422</v>
       </c>
       <c r="AB85" s="186" t="n">
         <v>762.5025427071794</v>
@@ -8952,10 +8952,10 @@
         <v>802.3695599371401</v>
       </c>
       <c r="AD85" s="188" t="n">
-        <v>84653902.06009358</v>
+        <v>84653902.06009357</v>
       </c>
       <c r="AE85" s="189" t="n">
-        <v>98592103.46307364</v>
+        <v>98592103.46307363</v>
       </c>
       <c r="AF85" s="189" t="n">
         <v>113804096.2813942</v>
@@ -9296,7 +9296,7 @@
         <v>151993.8782973449</v>
       </c>
       <c r="H90" s="74" t="n">
-        <v>1006.146929380826</v>
+        <v>1006.14692937085</v>
       </c>
       <c r="I90" s="75" t="n">
         <v>804.0973447741715</v>
@@ -9311,16 +9311,16 @@
         <v>64.82941274626535</v>
       </c>
       <c r="M90" s="74" t="n">
-        <v>107772.4246307993</v>
+        <v>107772.4246307893</v>
       </c>
       <c r="N90" s="75" t="n">
-        <v>118125.1139311579</v>
+        <v>118125.113931158</v>
       </c>
       <c r="O90" s="75" t="n">
         <v>127795.9679666604</v>
       </c>
       <c r="P90" s="75" t="n">
-        <v>137630.9353618428</v>
+        <v>137630.9353618429</v>
       </c>
       <c r="Q90" s="76" t="n">
         <v>152058.7077100912</v>
@@ -9331,7 +9331,7 @@
         </is>
       </c>
       <c r="T90" s="74" t="n">
-        <v>103217.7745947546</v>
+        <v>103217.7745947545</v>
       </c>
       <c r="U90" s="75" t="n">
         <v>113421.7142898477</v>
@@ -9340,13 +9340,13 @@
         <v>122981.7056221328</v>
       </c>
       <c r="W90" s="75" t="n">
-        <v>132719.082775768</v>
+        <v>132719.0827757681</v>
       </c>
       <c r="X90" s="76" t="n">
         <v>146942.1825658484</v>
       </c>
       <c r="Y90" s="74" t="n">
-        <v>810.6914425125003</v>
+        <v>810.6914425044615</v>
       </c>
       <c r="Z90" s="75" t="n">
         <v>647.8922882134144</v>
@@ -9361,13 +9361,13 @@
         <v>52.23556182679105</v>
       </c>
       <c r="AD90" s="74" t="n">
-        <v>104028.4660372671</v>
+        <v>104028.466037259</v>
       </c>
       <c r="AE90" s="75" t="n">
         <v>114069.6065780611</v>
       </c>
       <c r="AF90" s="75" t="n">
-        <v>123454.1093953308</v>
+        <v>123454.1093953309</v>
       </c>
       <c r="AG90" s="75" t="n">
         <v>133000.3902538578</v>
@@ -9437,7 +9437,7 @@
         <v>23109.32402884223</v>
       </c>
       <c r="N91" s="80" t="n">
-        <v>24649.62194193909</v>
+        <v>24649.6219419391</v>
       </c>
       <c r="O91" s="80" t="n">
         <v>26328.32544767897</v>
@@ -9457,7 +9457,7 @@
         <v>22594.04452840141</v>
       </c>
       <c r="U91" s="80" t="n">
-        <v>24157.15591258024</v>
+        <v>24157.15591258025</v>
       </c>
       <c r="V91" s="80" t="n">
         <v>25860.16669273701</v>
@@ -9533,13 +9533,13 @@
         <v>153387.0260951633</v>
       </c>
       <c r="F92" s="86" t="n">
-        <v>165383.5545780268</v>
+        <v>165383.5545780269</v>
       </c>
       <c r="G92" s="87" t="n">
         <v>182927.279593835</v>
       </c>
       <c r="H92" s="85" t="n">
-        <v>1244.296913314266</v>
+        <v>1244.296913304289</v>
       </c>
       <c r="I92" s="86" t="n">
         <v>1000.261358359291</v>
@@ -9554,10 +9554,10 @@
         <v>108.0055610889366</v>
       </c>
       <c r="M92" s="85" t="n">
-        <v>130881.7486596416</v>
+        <v>130881.7486596316</v>
       </c>
       <c r="N92" s="86" t="n">
-        <v>142774.735873097</v>
+        <v>142774.7358730971</v>
       </c>
       <c r="O92" s="86" t="n">
         <v>154124.2934143394</v>
@@ -9589,7 +9589,7 @@
         <v>177500.7645142633</v>
       </c>
       <c r="Y92" s="85" t="n">
-        <v>1048.022775568631</v>
+        <v>1048.022775560592</v>
       </c>
       <c r="Z92" s="86" t="n">
         <v>843.3819795115214</v>
@@ -9604,7 +9604,7 @@
         <v>95.26329029079685</v>
       </c>
       <c r="AD92" s="85" t="n">
-        <v>126859.8418987246</v>
+        <v>126859.8418987165</v>
       </c>
       <c r="AE92" s="86" t="n">
         <v>138422.2521819394</v>
@@ -9636,7 +9636,7 @@
         </is>
       </c>
       <c r="C93" s="79" t="n">
-        <v>8091.785240012696</v>
+        <v>8091.785240012697</v>
       </c>
       <c r="D93" s="80" t="n">
         <v>8842.409392020809</v>
@@ -9666,7 +9666,7 @@
         <v>0</v>
       </c>
       <c r="M93" s="79" t="n">
-        <v>8130.108560447517</v>
+        <v>8130.108560447518</v>
       </c>
       <c r="N93" s="80" t="n">
         <v>8867.363591213913</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="T93" s="79" t="n">
-        <v>6597.473818764502</v>
+        <v>6597.473818764503</v>
       </c>
       <c r="U93" s="80" t="n">
         <v>7209.480074951061</v>
@@ -9716,7 +9716,7 @@
         <v>0</v>
       </c>
       <c r="AD93" s="79" t="n">
-        <v>6631.302278710199</v>
+        <v>6631.3022787102</v>
       </c>
       <c r="AE93" s="80" t="n">
         <v>7231.507449361809</v>
@@ -9765,13 +9765,13 @@
         <v>163062.1958421902</v>
       </c>
       <c r="F94" s="86" t="n">
-        <v>176029.69319653</v>
+        <v>176029.6931965301</v>
       </c>
       <c r="G94" s="87" t="n">
         <v>194985.542673434</v>
       </c>
       <c r="H94" s="85" t="n">
-        <v>1282.620233749088</v>
+        <v>1282.620233739111</v>
       </c>
       <c r="I94" s="86" t="n">
         <v>1025.215557552396</v>
@@ -9786,10 +9786,10 @@
         <v>108.0055610889366</v>
       </c>
       <c r="M94" s="85" t="n">
-        <v>139011.8572200891</v>
+        <v>139011.8572200791</v>
       </c>
       <c r="N94" s="86" t="n">
-        <v>151642.0994643109</v>
+        <v>151642.099464311</v>
       </c>
       <c r="O94" s="86" t="n">
         <v>163809.305024764</v>
@@ -9812,7 +9812,7 @@
         <v>144788.350277379</v>
       </c>
       <c r="V94" s="86" t="n">
-        <v>156730.326741771</v>
+        <v>156730.3267417711</v>
       </c>
       <c r="W94" s="86" t="n">
         <v>169160.4379557467</v>
@@ -9821,7 +9821,7 @@
         <v>187332.2260036323</v>
       </c>
       <c r="Y94" s="85" t="n">
-        <v>1081.851235514328</v>
+        <v>1081.851235506289</v>
       </c>
       <c r="Z94" s="86" t="n">
         <v>865.4093539222695</v>
@@ -9836,7 +9836,7 @@
         <v>95.26329029079685</v>
       </c>
       <c r="AD94" s="85" t="n">
-        <v>133491.1441774348</v>
+        <v>133491.1441774268</v>
       </c>
       <c r="AE94" s="86" t="n">
         <v>145653.7596313012</v>
@@ -9994,7 +9994,7 @@
         <v>152110.7975908329</v>
       </c>
       <c r="E96" s="133" t="n">
-        <v>164632.5371995056</v>
+        <v>164632.5371995057</v>
       </c>
       <c r="F96" s="133" t="n">
         <v>177804.9021129451</v>
@@ -10003,7 +10003,7 @@
         <v>196971.3031150725</v>
       </c>
       <c r="H96" s="132" t="n">
-        <v>1284.783915559088</v>
+        <v>1284.783915549111</v>
       </c>
       <c r="I96" s="133" t="n">
         <v>1027.435451812396</v>
@@ -10012,13 +10012,13 @@
         <v>749.3965394237981</v>
       </c>
       <c r="K96" s="133" t="n">
-        <v>453.0339186077844</v>
+        <v>453.0339186077845</v>
       </c>
       <c r="L96" s="134" t="n">
         <v>110.3866338689366</v>
       </c>
       <c r="M96" s="132" t="n">
-        <v>140418.7030664032</v>
+        <v>140418.7030663932</v>
       </c>
       <c r="N96" s="133" t="n">
         <v>153138.2330426453</v>
@@ -10027,7 +10027,7 @@
         <v>165381.9337389295</v>
       </c>
       <c r="P96" s="133" t="n">
-        <v>178257.9360315528</v>
+        <v>178257.9360315529</v>
       </c>
       <c r="Q96" s="134" t="n">
         <v>197081.6897489414</v>
@@ -10053,7 +10053,7 @@
         <v>189771.324196888</v>
       </c>
       <c r="Y96" s="135" t="n">
-        <v>1084.42625463546</v>
+        <v>1084.426254627421</v>
       </c>
       <c r="Z96" s="136" t="n">
         <v>868.0512720360937</v>
@@ -10068,7 +10068,7 @@
         <v>98.0970285553463</v>
       </c>
       <c r="AD96" s="135" t="n">
-        <v>135219.0822653829</v>
+        <v>135219.0822653748</v>
       </c>
       <c r="AE96" s="136" t="n">
         <v>147491.3671833861</v>
